--- a/question_bank/ENGLISH.xlsx
+++ b/question_bank/ENGLISH.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Backup\D K Patra New\1 IMPORTANT\RKM Admission\PYTHON\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Backup\D K Patra New\1 IMPORTANT\RKM Admission\PYTHON\question_bank\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7500" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7500" firstSheet="16" activeTab="19"/>
   </bookViews>
   <sheets>
     <sheet name="Index" sheetId="14" r:id="rId1"/>
@@ -31,8 +31,10 @@
     <sheet name="Correct Spelling" sheetId="12" r:id="rId17"/>
     <sheet name="Correct Sentences" sheetId="15" r:id="rId18"/>
     <sheet name="Jumble Words" sheetId="13" r:id="rId19"/>
+    <sheet name="Comparison of Adjectives" sheetId="23" r:id="rId20"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'Comparison of Adjectives'!$A$1:$B$70</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Direct - Indirect 1'!$A$1:$B$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Direct - Indirect 2'!$A$1:$B$21</definedName>
   </definedNames>
@@ -46,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1678" uniqueCount="1609">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1818" uniqueCount="1747">
   <si>
     <t>Amazing</t>
   </si>
@@ -5123,9 +5125,6 @@
   </si>
   <si>
     <t>Adverb</t>
-  </si>
-  <si>
-    <t>Adjective</t>
   </si>
   <si>
     <t>Jumple Words</t>
@@ -8601,6 +8600,423 @@
   </si>
   <si>
     <t>An assembly of listeners</t>
+  </si>
+  <si>
+    <t>Positive</t>
+  </si>
+  <si>
+    <t>Bold (সাহসী)</t>
+  </si>
+  <si>
+    <t>Cold (ঠান্ডা)</t>
+  </si>
+  <si>
+    <t>Old (পারিবারিক সম্পর্কে বড়)</t>
+  </si>
+  <si>
+    <t>Clever (চতুর)</t>
+  </si>
+  <si>
+    <t>Few (অল্প কয়েকটি)</t>
+  </si>
+  <si>
+    <t>Great (মহান)</t>
+  </si>
+  <si>
+    <t>Hard (কঠিন)</t>
+  </si>
+  <si>
+    <t>High (উঁচু)</t>
+  </si>
+  <si>
+    <t>Kind (দয়ালু )</t>
+  </si>
+  <si>
+    <t>Low (নীচু</t>
+  </si>
+  <si>
+    <t>Long (লম্বা)</t>
+  </si>
+  <si>
+    <t>Poor (দরিদ্র)</t>
+  </si>
+  <si>
+    <t>Rich (ধনী)</t>
+  </si>
+  <si>
+    <t>Short (বেঁটে, খাটো)</t>
+  </si>
+  <si>
+    <t>Small (ছোট)</t>
+  </si>
+  <si>
+    <t>Strong (বলবান)</t>
+  </si>
+  <si>
+    <t>Soft (নরম)</t>
+  </si>
+  <si>
+    <t>Sweet (মিষ্ট)</t>
+  </si>
+  <si>
+    <t>Tall (লম্বা)</t>
+  </si>
+  <si>
+    <t>Weak (দুর্বল)</t>
+  </si>
+  <si>
+    <t>Able (সক্ষম )</t>
+  </si>
+  <si>
+    <t>Brave (সাহসী)</t>
+  </si>
+  <si>
+    <t>Fine (সুন্দর, পাতলা)</t>
+  </si>
+  <si>
+    <t>Late (সময় সম্পর্কে পরবর্তী)</t>
+  </si>
+  <si>
+    <t>Late (ক্রমসম্পর্কে পরবর্তী)</t>
+  </si>
+  <si>
+    <t>Large (বড়)</t>
+  </si>
+  <si>
+    <t>Noble (মহৎ)</t>
+  </si>
+  <si>
+    <t>Pale (বিবর্ণ )</t>
+  </si>
+  <si>
+    <t>True (সত্য)</t>
+  </si>
+  <si>
+    <t>Wise (জ্ঞানী)</t>
+  </si>
+  <si>
+    <t>White (সাদা)</t>
+  </si>
+  <si>
+    <t>Big (বড়)</t>
+  </si>
+  <si>
+    <t>Fat (মোটা)</t>
+  </si>
+  <si>
+    <t>Hot (গরম)</t>
+  </si>
+  <si>
+    <t>Mad (পাগল)</t>
+  </si>
+  <si>
+    <t>Sad (বিষণ্ণ )</t>
+  </si>
+  <si>
+    <t>Thin (পাতলা)</t>
+  </si>
+  <si>
+    <t>Thick</t>
+  </si>
+  <si>
+    <t>Busy (ব্যস্ত )</t>
+  </si>
+  <si>
+    <t>Easy (সহজ)</t>
+  </si>
+  <si>
+    <t>Dry (শুষ্ক)</t>
+  </si>
+  <si>
+    <t>Happy (সুখী)</t>
+  </si>
+  <si>
+    <t>Heavy (ভারী)</t>
+  </si>
+  <si>
+    <t>Holy (পবিত্র)</t>
+  </si>
+  <si>
+    <t>Merry (আনন্দিত)</t>
+  </si>
+  <si>
+    <t>Mighty (শক্তিশালী)</t>
+  </si>
+  <si>
+    <t>Ugly (কুশ্রী)</t>
+  </si>
+  <si>
+    <t>Wealthy (সম্পদশালী)</t>
+  </si>
+  <si>
+    <t>Gay (আনন্দিত)</t>
+  </si>
+  <si>
+    <t>Grey (ধূসর)</t>
+  </si>
+  <si>
+    <t>Good (ভালো)</t>
+  </si>
+  <si>
+    <t>Bad ( মন্দ)</t>
+  </si>
+  <si>
+    <t>Far (দুর)</t>
+  </si>
+  <si>
+    <t>Fore (আরো)</t>
+  </si>
+  <si>
+    <t>Little (কম)</t>
+  </si>
+  <si>
+    <t>Much (বেশি)</t>
+  </si>
+  <si>
+    <t>Many (অনেক)</t>
+  </si>
+  <si>
+    <t>Diligent (পরিশ্রমী</t>
+  </si>
+  <si>
+    <t>Important (গুরুত্বপূর্ণ)</t>
+  </si>
+  <si>
+    <t>Intelligent (বুদ্ধিমান)</t>
+  </si>
+  <si>
+    <t>Industrious (অধ্যবসায়ী)</t>
+  </si>
+  <si>
+    <t>Learned (শিক্ষিত)</t>
+  </si>
+  <si>
+    <t>Beautiful (সুন্দর)</t>
+  </si>
+  <si>
+    <t>Dutiful (কর্তব্যপরায়ণ</t>
+  </si>
+  <si>
+    <t>Courageous (সাহসী)</t>
+  </si>
+  <si>
+    <t>Difficult (কঠিন)</t>
+  </si>
+  <si>
+    <t>Careful</t>
+  </si>
+  <si>
+    <t>Old (বয়সে বড়, পুরাতন)</t>
+  </si>
+  <si>
+    <t>Comparison of Adjectives</t>
+  </si>
+  <si>
+    <t>Comparative | Superlative</t>
+  </si>
+  <si>
+    <t>bolder | boldest</t>
+  </si>
+  <si>
+    <t>colder | coldest</t>
+  </si>
+  <si>
+    <t>older | oldest</t>
+  </si>
+  <si>
+    <t>elder | eldest</t>
+  </si>
+  <si>
+    <t>cleverer | cleverest</t>
+  </si>
+  <si>
+    <t>fewer | fewest</t>
+  </si>
+  <si>
+    <t>greater | greatest</t>
+  </si>
+  <si>
+    <t>harder | hardest</t>
+  </si>
+  <si>
+    <t>higher | highest</t>
+  </si>
+  <si>
+    <t>kinder | kindest</t>
+  </si>
+  <si>
+    <t>lower | lowest</t>
+  </si>
+  <si>
+    <t>longer | longest</t>
+  </si>
+  <si>
+    <t>poorer | poorest</t>
+  </si>
+  <si>
+    <t>richer | richest</t>
+  </si>
+  <si>
+    <t>shorter | shortest</t>
+  </si>
+  <si>
+    <t>smaller | smallest</t>
+  </si>
+  <si>
+    <t>stronger | strongest</t>
+  </si>
+  <si>
+    <t>softer | softest</t>
+  </si>
+  <si>
+    <t>sweeter | sweetest</t>
+  </si>
+  <si>
+    <t>taller | tallest</t>
+  </si>
+  <si>
+    <t>weaker | weakest</t>
+  </si>
+  <si>
+    <t>abler | ablest</t>
+  </si>
+  <si>
+    <t>braver | bravest</t>
+  </si>
+  <si>
+    <t>finer | finest</t>
+  </si>
+  <si>
+    <t>later | latest</t>
+  </si>
+  <si>
+    <t>Latter | last</t>
+  </si>
+  <si>
+    <t>larger | largest</t>
+  </si>
+  <si>
+    <t>nobler | noblest</t>
+  </si>
+  <si>
+    <t>paler | palest</t>
+  </si>
+  <si>
+    <t>truer | truest</t>
+  </si>
+  <si>
+    <t>wiser | wisest</t>
+  </si>
+  <si>
+    <t>whiter | whitest</t>
+  </si>
+  <si>
+    <t>bigger | biggest</t>
+  </si>
+  <si>
+    <t>fatter | fattest</t>
+  </si>
+  <si>
+    <t>hotter | hottest</t>
+  </si>
+  <si>
+    <t>madder | maddest</t>
+  </si>
+  <si>
+    <t>sadder | saddest</t>
+  </si>
+  <si>
+    <t>thinner | thinnest</t>
+  </si>
+  <si>
+    <t>thicker | thickest</t>
+  </si>
+  <si>
+    <t>cooler | coolest</t>
+  </si>
+  <si>
+    <t>busier | busiest</t>
+  </si>
+  <si>
+    <t>easier | easiest</t>
+  </si>
+  <si>
+    <t>drier | driest</t>
+  </si>
+  <si>
+    <t>happier | happiest</t>
+  </si>
+  <si>
+    <t>heavier | heaviest</t>
+  </si>
+  <si>
+    <t>holier | holiest</t>
+  </si>
+  <si>
+    <t>merrier | merriest</t>
+  </si>
+  <si>
+    <t>mightier | mightiest</t>
+  </si>
+  <si>
+    <t>uglier | ugliest</t>
+  </si>
+  <si>
+    <t>wealthier | wealthiest</t>
+  </si>
+  <si>
+    <t>gayer | gayest</t>
+  </si>
+  <si>
+    <t>greyer | greyest</t>
+  </si>
+  <si>
+    <t>better | best</t>
+  </si>
+  <si>
+    <t>worse | worst</t>
+  </si>
+  <si>
+    <t>farther | farthest</t>
+  </si>
+  <si>
+    <t>further / furthermore | furthest/furthermost</t>
+  </si>
+  <si>
+    <t>less | least</t>
+  </si>
+  <si>
+    <t>more | most</t>
+  </si>
+  <si>
+    <t>more beautiful | most beautiful</t>
+  </si>
+  <si>
+    <t>more dutiful | most dutiful</t>
+  </si>
+  <si>
+    <t>more careful/less careful | most careful/least careful</t>
+  </si>
+  <si>
+    <t>more courageous | most courageous</t>
+  </si>
+  <si>
+    <t>more difficult | most difficult</t>
+  </si>
+  <si>
+    <t>more diligent | most diligent</t>
+  </si>
+  <si>
+    <t>more important | most important</t>
+  </si>
+  <si>
+    <t>more intelligent | most intelligent</t>
+  </si>
+  <si>
+    <t>more industrious | most industrious</t>
+  </si>
+  <si>
+    <t>more learned | most learned may</t>
   </si>
 </sst>
 </file>
@@ -9200,7 +9616,7 @@
   <sheetData>
     <row r="2" spans="2:2">
       <c r="B2" s="1" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
     </row>
     <row r="3" spans="2:2">
@@ -9228,7 +9644,7 @@
     </row>
     <row r="8" spans="2:2" s="2" customFormat="1">
       <c r="B8" s="1" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
     </row>
     <row r="9" spans="2:2">
@@ -9258,7 +9674,7 @@
     </row>
     <row r="14" spans="2:2">
       <c r="B14" s="7" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="16" spans="2:2">
@@ -9268,7 +9684,7 @@
     </row>
     <row r="17" spans="2:2">
       <c r="B17" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
     </row>
     <row r="18" spans="2:2">
@@ -9283,7 +9699,7 @@
     </row>
     <row r="20" spans="2:2">
       <c r="B20" s="7" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="21" spans="2:2">
@@ -9302,8 +9718,8 @@
       </c>
     </row>
     <row r="24" spans="2:2">
-      <c r="B24" t="s">
-        <v>916</v>
+      <c r="B24" s="7" t="s">
+        <v>1677</v>
       </c>
     </row>
     <row r="25" spans="2:2">
@@ -9323,7 +9739,7 @@
     </row>
     <row r="30" spans="2:2">
       <c r="B30" s="7" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
     </row>
   </sheetData>
@@ -9344,6 +9760,7 @@
     <hyperlink ref="B20" location="Article!A1" display="Article"/>
     <hyperlink ref="B21" location="Preposition!A1" display="Preposition"/>
     <hyperlink ref="B18" location="'Convert to Abstarct Noun'!A1" display="Noun"/>
+    <hyperlink ref="B24" location="'Comparison of Adjectives'!A1" display="Comparison of Adjectives"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -10077,138 +10494,138 @@
     </row>
     <row r="2" spans="1:2" ht="15.75">
       <c r="A2" s="8" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15.75">
       <c r="A3" s="8" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15.75">
       <c r="A4" s="8" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15.75">
       <c r="A5" s="8" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="15.75">
       <c r="A6" s="8" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="15.75">
       <c r="A7" s="8" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="15.75">
       <c r="A8" s="8" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="15.75">
       <c r="A9" s="8" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="15.75">
       <c r="A10" s="8" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="15.75">
       <c r="A11" s="8" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="15.75">
       <c r="A12" s="8" t="s">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>1282</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="15.75">
       <c r="A13" s="8" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="15.75">
       <c r="A14" s="8" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>1284</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="15.75">
       <c r="A15" s="8" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="15.75">
       <c r="A16" s="8" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="15.75">
       <c r="A17" s="8" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="8" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="B18" s="22" t="s">
-        <v>1288</v>
+        <v>1287</v>
       </c>
     </row>
   </sheetData>
@@ -10238,226 +10655,226 @@
     </row>
     <row r="2" spans="1:2" ht="15.75">
       <c r="A2" s="8" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15.75">
       <c r="A3" s="8" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15.75">
       <c r="A4" s="8" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15.75">
       <c r="A5" s="8" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>1292</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="15.75">
       <c r="A6" s="8" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="15.75">
       <c r="A7" s="8" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="15.75">
       <c r="A8" s="8" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="15.75">
       <c r="A9" s="8" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>1296</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="15.75">
       <c r="A10" s="8" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="15.75">
       <c r="A11" s="8" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="15.75">
       <c r="A12" s="8" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="15.75">
       <c r="A13" s="8" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="15.75">
       <c r="A14" s="8" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="15.75">
       <c r="A15" s="8" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="15.75">
       <c r="A16" s="8" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>1303</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="15.75">
       <c r="A17" s="8" t="s">
-        <v>1259</v>
+        <v>1258</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>1304</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="15.75">
       <c r="A18" s="8" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>1305</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="15.75">
       <c r="A19" s="8" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>1306</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="15.75">
       <c r="A20" s="8" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>1307</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="15.75">
       <c r="A21" s="8" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="15.75">
       <c r="A22" s="8" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="15.75">
       <c r="A23" s="8" t="s">
-        <v>1265</v>
+        <v>1264</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="15.75">
       <c r="A24" s="8" t="s">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="15.75">
       <c r="A25" s="8" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="15.75">
       <c r="A26" s="8" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="15.75">
       <c r="A27" s="8" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>1314</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="15.75">
       <c r="A28" s="8" t="s">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>1315</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="15.75">
       <c r="A29" s="8" t="s">
-        <v>1271</v>
+        <v>1270</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>1316</v>
+        <v>1315</v>
       </c>
     </row>
   </sheetData>
@@ -10506,658 +10923,658 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="45" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B2" s="45" t="s">
         <v>1139</v>
-      </c>
-      <c r="B2" s="45" t="s">
-        <v>1140</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="45" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B3" s="45" t="s">
         <v>1141</v>
-      </c>
-      <c r="B3" s="45" t="s">
-        <v>1142</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="45" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B4" s="45" t="s">
         <v>1143</v>
-      </c>
-      <c r="B4" s="45" t="s">
-        <v>1144</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="45" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B5" s="45" t="s">
         <v>1145</v>
-      </c>
-      <c r="B5" s="45" t="s">
-        <v>1146</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="45" t="s">
+        <v>1146</v>
+      </c>
+      <c r="B6" s="45" t="s">
         <v>1147</v>
-      </c>
-      <c r="B6" s="45" t="s">
-        <v>1148</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="45" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B7" s="45" t="s">
         <v>1149</v>
-      </c>
-      <c r="B7" s="45" t="s">
-        <v>1150</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="45" t="s">
+        <v>1150</v>
+      </c>
+      <c r="B8" s="45" t="s">
         <v>1151</v>
-      </c>
-      <c r="B8" s="45" t="s">
-        <v>1152</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="45" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B9" s="45" t="s">
         <v>1153</v>
-      </c>
-      <c r="B9" s="45" t="s">
-        <v>1154</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="45" t="s">
+        <v>1154</v>
+      </c>
+      <c r="B10" s="45" t="s">
         <v>1155</v>
-      </c>
-      <c r="B10" s="45" t="s">
-        <v>1156</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="45" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B11" s="45" t="s">
         <v>1157</v>
-      </c>
-      <c r="B11" s="45" t="s">
-        <v>1158</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="45" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B12" s="45" t="s">
         <v>1159</v>
-      </c>
-      <c r="B12" s="45" t="s">
-        <v>1160</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="15.75" thickBot="1">
       <c r="A13" s="46" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B13" s="46" t="s">
         <v>1161</v>
-      </c>
-      <c r="B13" s="46" t="s">
-        <v>1162</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="45" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="B14" s="45" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="45" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="B15" s="45" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="45" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
       <c r="B16" s="45" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="45" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="B17" s="45" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="45" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="B18" s="45" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="45" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="B19" s="45" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="45" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="B20" s="45" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="45" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="B21" s="45" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="45" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="B22" s="45" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="45" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="B23" s="45" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="45" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="B24" s="45" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="45" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="B25" s="45" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="45" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="B26" s="45" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="45" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="B27" s="45" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="45" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="B28" s="45" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="45" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="B29" s="45" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="45" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="B30" s="45" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="45" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="B31" s="45" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="45" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="B32" s="45" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="45" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="B33" s="45" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="45" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="B34" s="45" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="45" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="B35" s="45" t="s">
-        <v>1363</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="45" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="B36" s="45" t="s">
-        <v>1364</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="45" t="s">
-        <v>1092</v>
+        <v>1091</v>
       </c>
       <c r="B37" s="45" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="45" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="B38" s="45" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="45" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="B39" s="45" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="45" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="B40" s="45" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="45" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="B41" s="45" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="45" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="B42" s="45" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="45" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="B43" s="45" t="s">
-        <v>1190</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="45" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="B44" s="45" t="s">
-        <v>1191</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="45" t="s">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="B45" s="45" t="s">
-        <v>1365</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="45" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="B46" s="45" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="45" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="B47" s="45" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="45" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="B48" s="45" t="s">
-        <v>1366</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="45" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="B49" s="45" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="45" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="B50" s="45" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="45" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="B51" s="45" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="45" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="B52" s="45" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="45" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="B53" s="45" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="45" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="B54" s="47" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="45" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="B55" s="47" t="s">
-        <v>1199</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="45" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="B56" s="47" t="s">
-        <v>1200</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="45" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="B57" s="47" t="s">
-        <v>1201</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="45" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="B58" s="47" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="45" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="B59" s="47" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="45" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="B60" s="47" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="45" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="B61" s="47" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="45" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="B62" s="47" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="45" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="B63" s="47" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="45" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="B64" s="47" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="45" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="B65" s="47" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="45" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="B66" s="47" t="s">
-        <v>1210</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="45" t="s">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="B67" s="47" t="s">
-        <v>1211</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="45" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="B68" s="43" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="45" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="B69" s="45" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="45" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="B70" s="45" t="s">
-        <v>1368</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="45" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="B71" s="45" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="45" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="B72" s="45" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="45" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="B73" s="45" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="45" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
       <c r="B74" s="45" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="45" t="s">
-        <v>1130</v>
+        <v>1129</v>
       </c>
       <c r="B75" s="45" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="45" t="s">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="B76" s="45" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="45" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="B77" s="45" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="45" t="s">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="B78" s="45" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="45" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="B79" s="45" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="45" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="B80" s="45" t="s">
-        <v>1222</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="45" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="B81" s="45" t="s">
-        <v>1223</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="45" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="B82" s="45" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="45" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="B83" s="44" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
     </row>
   </sheetData>
@@ -12236,6 +12653,585 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B70"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="27.5703125" style="33" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="49" style="33" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.140625" style="33"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="1" customFormat="1">
+      <c r="A1" s="10" t="s">
+        <v>1608</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1678</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="33" t="s">
+        <v>1609</v>
+      </c>
+      <c r="B2" s="33" t="s">
+        <v>1679</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="33" t="s">
+        <v>1610</v>
+      </c>
+      <c r="B3" s="33" t="s">
+        <v>1680</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="33" t="s">
+        <v>1676</v>
+      </c>
+      <c r="B4" s="33" t="s">
+        <v>1681</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="33" t="s">
+        <v>1611</v>
+      </c>
+      <c r="B5" s="33" t="s">
+        <v>1682</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="33" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B6" s="33" t="s">
+        <v>1683</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="33" t="s">
+        <v>1613</v>
+      </c>
+      <c r="B7" s="33" t="s">
+        <v>1684</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="33" t="s">
+        <v>1614</v>
+      </c>
+      <c r="B8" s="33" t="s">
+        <v>1685</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="33" t="s">
+        <v>1615</v>
+      </c>
+      <c r="B9" s="33" t="s">
+        <v>1686</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="33" t="s">
+        <v>1616</v>
+      </c>
+      <c r="B10" s="33" t="s">
+        <v>1687</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="33" t="s">
+        <v>1617</v>
+      </c>
+      <c r="B11" s="33" t="s">
+        <v>1688</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="33" t="s">
+        <v>1618</v>
+      </c>
+      <c r="B12" s="33" t="s">
+        <v>1689</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="33" t="s">
+        <v>1619</v>
+      </c>
+      <c r="B13" s="33" t="s">
+        <v>1690</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="33" t="s">
+        <v>1620</v>
+      </c>
+      <c r="B14" s="33" t="s">
+        <v>1691</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="33" t="s">
+        <v>1621</v>
+      </c>
+      <c r="B15" s="33" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="33" t="s">
+        <v>1622</v>
+      </c>
+      <c r="B16" s="33" t="s">
+        <v>1693</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="33" t="s">
+        <v>1623</v>
+      </c>
+      <c r="B17" s="33" t="s">
+        <v>1694</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="33" t="s">
+        <v>1624</v>
+      </c>
+      <c r="B18" s="33" t="s">
+        <v>1695</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="33" t="s">
+        <v>1625</v>
+      </c>
+      <c r="B19" s="33" t="s">
+        <v>1696</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="33" t="s">
+        <v>1626</v>
+      </c>
+      <c r="B20" s="33" t="s">
+        <v>1697</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="33" t="s">
+        <v>1627</v>
+      </c>
+      <c r="B21" s="33" t="s">
+        <v>1698</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="33" t="s">
+        <v>1628</v>
+      </c>
+      <c r="B22" s="33" t="s">
+        <v>1699</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="33" t="s">
+        <v>1629</v>
+      </c>
+      <c r="B23" s="33" t="s">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="33" t="s">
+        <v>1630</v>
+      </c>
+      <c r="B24" s="33" t="s">
+        <v>1701</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="33" t="s">
+        <v>1631</v>
+      </c>
+      <c r="B25" s="33" t="s">
+        <v>1702</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="33" t="s">
+        <v>1632</v>
+      </c>
+      <c r="B26" s="33" t="s">
+        <v>1703</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="33" t="s">
+        <v>1633</v>
+      </c>
+      <c r="B27" s="33" t="s">
+        <v>1704</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" s="33" t="s">
+        <v>1634</v>
+      </c>
+      <c r="B28" s="33" t="s">
+        <v>1705</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" s="33" t="s">
+        <v>1635</v>
+      </c>
+      <c r="B29" s="33" t="s">
+        <v>1706</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" s="33" t="s">
+        <v>1636</v>
+      </c>
+      <c r="B30" s="33" t="s">
+        <v>1707</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" s="33" t="s">
+        <v>1637</v>
+      </c>
+      <c r="B31" s="33" t="s">
+        <v>1708</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" s="33" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B32" s="33" t="s">
+        <v>1709</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="33" t="s">
+        <v>1639</v>
+      </c>
+      <c r="B33" s="33" t="s">
+        <v>1710</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" s="33" t="s">
+        <v>1640</v>
+      </c>
+      <c r="B34" s="33" t="s">
+        <v>1711</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" s="33" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B35" s="33" t="s">
+        <v>1712</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" s="33" t="s">
+        <v>1642</v>
+      </c>
+      <c r="B36" s="33" t="s">
+        <v>1713</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" s="33" t="s">
+        <v>1643</v>
+      </c>
+      <c r="B37" s="33" t="s">
+        <v>1714</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" s="33" t="s">
+        <v>1644</v>
+      </c>
+      <c r="B38" s="33" t="s">
+        <v>1715</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" s="33" t="s">
+        <v>1645</v>
+      </c>
+      <c r="B39" s="33" t="s">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" s="33" t="s">
+        <v>1646</v>
+      </c>
+      <c r="B40" s="33" t="s">
+        <v>1717</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" s="33" t="s">
+        <v>250</v>
+      </c>
+      <c r="B41" s="33" t="s">
+        <v>1718</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" s="33" t="s">
+        <v>1647</v>
+      </c>
+      <c r="B42" s="33" t="s">
+        <v>1719</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" s="33" t="s">
+        <v>1648</v>
+      </c>
+      <c r="B43" s="33" t="s">
+        <v>1720</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" s="33" t="s">
+        <v>1649</v>
+      </c>
+      <c r="B44" s="33" t="s">
+        <v>1721</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" s="33" t="s">
+        <v>1650</v>
+      </c>
+      <c r="B45" s="33" t="s">
+        <v>1722</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" s="33" t="s">
+        <v>1651</v>
+      </c>
+      <c r="B46" s="33" t="s">
+        <v>1723</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" s="33" t="s">
+        <v>1652</v>
+      </c>
+      <c r="B47" s="33" t="s">
+        <v>1724</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" s="33" t="s">
+        <v>1653</v>
+      </c>
+      <c r="B48" s="33" t="s">
+        <v>1725</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" s="33" t="s">
+        <v>1654</v>
+      </c>
+      <c r="B49" s="33" t="s">
+        <v>1726</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" s="33" t="s">
+        <v>1655</v>
+      </c>
+      <c r="B50" s="33" t="s">
+        <v>1727</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" s="33" t="s">
+        <v>1656</v>
+      </c>
+      <c r="B51" s="33" t="s">
+        <v>1728</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" s="33" t="s">
+        <v>1657</v>
+      </c>
+      <c r="B52" s="33" t="s">
+        <v>1729</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" s="33" t="s">
+        <v>1658</v>
+      </c>
+      <c r="B53" s="33" t="s">
+        <v>1730</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" s="33" t="s">
+        <v>1659</v>
+      </c>
+      <c r="B54" s="33" t="s">
+        <v>1731</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" s="33" t="s">
+        <v>1660</v>
+      </c>
+      <c r="B55" s="33" t="s">
+        <v>1732</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" s="33" t="s">
+        <v>1661</v>
+      </c>
+      <c r="B56" s="33" t="s">
+        <v>1733</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" s="33" t="s">
+        <v>1662</v>
+      </c>
+      <c r="B57" s="33" t="s">
+        <v>1734</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" s="33" t="s">
+        <v>1663</v>
+      </c>
+      <c r="B58" s="33" t="s">
+        <v>1735</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" s="33" t="s">
+        <v>1664</v>
+      </c>
+      <c r="B59" s="33" t="s">
+        <v>1736</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" s="33" t="s">
+        <v>1665</v>
+      </c>
+      <c r="B60" s="33" t="s">
+        <v>1736</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" s="33" t="s">
+        <v>1671</v>
+      </c>
+      <c r="B61" s="33" t="s">
+        <v>1737</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" s="33" t="s">
+        <v>1672</v>
+      </c>
+      <c r="B62" s="33" t="s">
+        <v>1738</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63" s="33" t="s">
+        <v>1675</v>
+      </c>
+      <c r="B63" s="33" t="s">
+        <v>1739</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" s="33" t="s">
+        <v>1673</v>
+      </c>
+      <c r="B64" s="33" t="s">
+        <v>1740</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" s="33" t="s">
+        <v>1674</v>
+      </c>
+      <c r="B65" s="33" t="s">
+        <v>1741</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66" s="33" t="s">
+        <v>1666</v>
+      </c>
+      <c r="B66" s="33" t="s">
+        <v>1742</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67" s="33" t="s">
+        <v>1667</v>
+      </c>
+      <c r="B67" s="33" t="s">
+        <v>1743</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68" s="33" t="s">
+        <v>1668</v>
+      </c>
+      <c r="B68" s="33" t="s">
+        <v>1744</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69" s="33" t="s">
+        <v>1669</v>
+      </c>
+      <c r="B69" s="33" t="s">
+        <v>1745</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70" s="33" t="s">
+        <v>1670</v>
+      </c>
+      <c r="B70" s="33" t="s">
+        <v>1746</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:B70"/>
+  <hyperlinks>
+    <hyperlink ref="A1" location="Index!A1" display="Positive"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B62"/>
@@ -12761,39 +13757,39 @@
   <sheetData>
     <row r="1" spans="1:2" s="49" customFormat="1">
       <c r="A1" s="50" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="B1" s="50" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="51" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="B2" s="51" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="51" t="s">
+        <v>1558</v>
+      </c>
+      <c r="B3" s="51" t="s">
         <v>1559</v>
-      </c>
-      <c r="B3" s="51" t="s">
-        <v>1560</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="51" t="s">
-        <v>1569</v>
+        <v>1568</v>
       </c>
       <c r="B4" s="51" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="51" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="B5" s="51" t="s">
         <v>869</v>
@@ -12801,71 +13797,71 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="51" t="s">
+        <v>1562</v>
+      </c>
+      <c r="B6" s="51" t="s">
         <v>1563</v>
-      </c>
-      <c r="B6" s="51" t="s">
-        <v>1564</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="51" t="s">
-        <v>1608</v>
+        <v>1607</v>
       </c>
       <c r="B7" s="51" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="51" t="s">
+        <v>1565</v>
+      </c>
+      <c r="B8" s="51" t="s">
         <v>1566</v>
-      </c>
-      <c r="B8" s="51" t="s">
-        <v>1567</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="51" t="s">
-        <v>1568</v>
+        <v>1567</v>
       </c>
       <c r="B9" s="51" t="s">
-        <v>1570</v>
+        <v>1569</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="51" t="s">
+        <v>1570</v>
+      </c>
+      <c r="B10" s="51" t="s">
         <v>1571</v>
-      </c>
-      <c r="B10" s="51" t="s">
-        <v>1572</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="51" t="s">
+        <v>1572</v>
+      </c>
+      <c r="B11" s="51" t="s">
         <v>1573</v>
-      </c>
-      <c r="B11" s="51" t="s">
-        <v>1574</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="51" t="s">
+        <v>1574</v>
+      </c>
+      <c r="B12" s="51" t="s">
         <v>1575</v>
-      </c>
-      <c r="B12" s="51" t="s">
-        <v>1576</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="51" t="s">
+        <v>1576</v>
+      </c>
+      <c r="B13" s="51" t="s">
         <v>1577</v>
-      </c>
-      <c r="B13" s="51" t="s">
-        <v>1578</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="51" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="B14" s="51" t="s">
         <v>128</v>
@@ -12873,15 +13869,15 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="51" t="s">
+        <v>1579</v>
+      </c>
+      <c r="B15" s="51" t="s">
         <v>1580</v>
-      </c>
-      <c r="B15" s="51" t="s">
-        <v>1581</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="51" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="B16" s="51" t="s">
         <v>891</v>
@@ -12889,87 +13885,87 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="51" t="s">
+        <v>1582</v>
+      </c>
+      <c r="B17" s="51" t="s">
         <v>1583</v>
-      </c>
-      <c r="B17" s="51" t="s">
-        <v>1584</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="51" t="s">
+        <v>1584</v>
+      </c>
+      <c r="B18" s="51" t="s">
         <v>1585</v>
-      </c>
-      <c r="B18" s="51" t="s">
-        <v>1586</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="51" t="s">
+        <v>1586</v>
+      </c>
+      <c r="B19" s="51" t="s">
         <v>1587</v>
-      </c>
-      <c r="B19" s="51" t="s">
-        <v>1588</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="51" t="s">
+        <v>1588</v>
+      </c>
+      <c r="B20" s="51" t="s">
         <v>1589</v>
-      </c>
-      <c r="B20" s="51" t="s">
-        <v>1590</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="51" t="s">
+        <v>1590</v>
+      </c>
+      <c r="B21" s="51" t="s">
         <v>1591</v>
-      </c>
-      <c r="B21" s="51" t="s">
-        <v>1592</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="51" t="s">
+        <v>1592</v>
+      </c>
+      <c r="B22" s="51" t="s">
         <v>1593</v>
-      </c>
-      <c r="B22" s="51" t="s">
-        <v>1594</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="51" t="s">
+        <v>1594</v>
+      </c>
+      <c r="B23" s="51" t="s">
         <v>1595</v>
-      </c>
-      <c r="B23" s="51" t="s">
-        <v>1596</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="51" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="B24" s="51" t="s">
-        <v>1600</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="51" t="s">
+        <v>1597</v>
+      </c>
+      <c r="B25" s="51" t="s">
         <v>1598</v>
-      </c>
-      <c r="B25" s="51" t="s">
-        <v>1599</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="51" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="B26" s="51" t="s">
-        <v>1601</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="51" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="B27" s="51" t="s">
         <v>900</v>
@@ -12977,18 +13973,18 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="51" t="s">
+        <v>1603</v>
+      </c>
+      <c r="B28" s="51" t="s">
         <v>1604</v>
-      </c>
-      <c r="B28" s="51" t="s">
-        <v>1605</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="51" t="s">
+        <v>1605</v>
+      </c>
+      <c r="B29" s="51" t="s">
         <v>1606</v>
-      </c>
-      <c r="B29" s="51" t="s">
-        <v>1607</v>
       </c>
     </row>
   </sheetData>
@@ -13008,7 +14004,7 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1">
       <c r="A1" s="27" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>591</v>
@@ -13016,26 +14012,26 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="28" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="B2" s="28" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="28" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="B3" s="28" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="28" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="B4" s="28" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="30">
@@ -13043,15 +14039,15 @@
         <v>252</v>
       </c>
       <c r="B5" s="28" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="28" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="B6" s="28" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -13059,12 +14055,12 @@
         <v>40</v>
       </c>
       <c r="B7" s="28" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="28" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="B8" s="28" t="s">
         <v>142</v>
@@ -13072,18 +14068,18 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="28" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="B9" s="28" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="28" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="B10" s="28" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -13091,12 +14087,12 @@
         <v>214</v>
       </c>
       <c r="B11" s="28" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="28" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="B12" s="28" t="s">
         <v>869</v>
@@ -13104,10 +14100,10 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="28" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="B13" s="28" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -13115,23 +14111,23 @@
         <v>137</v>
       </c>
       <c r="B14" s="28" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="28" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="B15" s="28" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="28" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="B16" s="28" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -13139,31 +14135,31 @@
         <v>220</v>
       </c>
       <c r="B17" s="28" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="28" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="B18" s="28" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="28" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="B19" s="28" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="28" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B20" s="28" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -13171,7 +14167,7 @@
         <v>307</v>
       </c>
       <c r="B21" s="28" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -13224,18 +14220,18 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="30" t="s">
+        <v>950</v>
+      </c>
+      <c r="B28" s="31" t="s">
         <v>951</v>
-      </c>
-      <c r="B28" s="31" t="s">
-        <v>952</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="30" t="s">
+        <v>952</v>
+      </c>
+      <c r="B29" s="31" t="s">
         <v>953</v>
-      </c>
-      <c r="B29" s="31" t="s">
-        <v>954</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -13243,12 +14239,12 @@
         <v>155</v>
       </c>
       <c r="B30" s="31" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="30" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="B31" s="31" t="s">
         <v>189</v>
@@ -13256,10 +14252,10 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="30" t="s">
+        <v>956</v>
+      </c>
+      <c r="B32" s="31" t="s">
         <v>957</v>
-      </c>
-      <c r="B32" s="31" t="s">
-        <v>958</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -13272,10 +14268,10 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="30" t="s">
+        <v>958</v>
+      </c>
+      <c r="B34" s="31" t="s">
         <v>959</v>
-      </c>
-      <c r="B34" s="31" t="s">
-        <v>960</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -13307,7 +14303,7 @@
         <v>198</v>
       </c>
       <c r="B38" s="31" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -13320,7 +14316,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="30" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="B40" s="31" t="s">
         <v>239</v>
@@ -13328,10 +14324,10 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="30" t="s">
+        <v>962</v>
+      </c>
+      <c r="B41" s="31" t="s">
         <v>963</v>
-      </c>
-      <c r="B41" s="31" t="s">
-        <v>964</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -13347,7 +14343,7 @@
         <v>179</v>
       </c>
       <c r="B43" s="31" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -13355,20 +14351,20 @@
         <v>185</v>
       </c>
       <c r="B44" s="31" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="30" t="s">
+        <v>966</v>
+      </c>
+      <c r="B45" s="31" t="s">
         <v>967</v>
-      </c>
-      <c r="B45" s="31" t="s">
-        <v>968</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="30" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B46" s="31" t="s">
         <v>230</v>
@@ -13379,15 +14375,15 @@
         <v>278</v>
       </c>
       <c r="B47" s="31" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="30" t="s">
+        <v>970</v>
+      </c>
+      <c r="B48" s="31" t="s">
         <v>971</v>
-      </c>
-      <c r="B48" s="31" t="s">
-        <v>972</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -13403,23 +14399,23 @@
         <v>204</v>
       </c>
       <c r="B50" s="31" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="30" t="s">
+        <v>973</v>
+      </c>
+      <c r="B51" s="31" t="s">
         <v>974</v>
-      </c>
-      <c r="B51" s="31" t="s">
-        <v>975</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="30" t="s">
+        <v>975</v>
+      </c>
+      <c r="B52" s="31" t="s">
         <v>976</v>
-      </c>
-      <c r="B52" s="31" t="s">
-        <v>977</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -13427,15 +14423,15 @@
         <v>208</v>
       </c>
       <c r="B53" s="31" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="30" t="s">
+        <v>978</v>
+      </c>
+      <c r="B54" s="31" t="s">
         <v>979</v>
-      </c>
-      <c r="B54" s="31" t="s">
-        <v>980</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -13443,7 +14439,7 @@
         <v>176</v>
       </c>
       <c r="B55" s="31" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -13451,15 +14447,15 @@
         <v>177</v>
       </c>
       <c r="B56" s="31" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="30" t="s">
+        <v>982</v>
+      </c>
+      <c r="B57" s="31" t="s">
         <v>983</v>
-      </c>
-      <c r="B57" s="31" t="s">
-        <v>984</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -13467,7 +14463,7 @@
         <v>163</v>
       </c>
       <c r="B58" s="31" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -13483,63 +14479,63 @@
         <v>218</v>
       </c>
       <c r="B60" s="31" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="30" t="s">
+        <v>986</v>
+      </c>
+      <c r="B61" s="31" t="s">
         <v>987</v>
-      </c>
-      <c r="B61" s="31" t="s">
-        <v>988</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="30" t="s">
+        <v>988</v>
+      </c>
+      <c r="B62" s="31" t="s">
         <v>989</v>
-      </c>
-      <c r="B62" s="31" t="s">
-        <v>990</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="30" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="B63" s="31" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="30" t="s">
+        <v>991</v>
+      </c>
+      <c r="B64" s="31" t="s">
         <v>992</v>
-      </c>
-      <c r="B64" s="31" t="s">
-        <v>993</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="30" t="s">
+        <v>993</v>
+      </c>
+      <c r="B65" s="31" t="s">
         <v>994</v>
-      </c>
-      <c r="B65" s="31" t="s">
-        <v>995</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="30" t="s">
+        <v>995</v>
+      </c>
+      <c r="B66" s="31" t="s">
         <v>996</v>
-      </c>
-      <c r="B66" s="31" t="s">
-        <v>997</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="30" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="B67" s="31" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -13552,18 +14548,18 @@
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="30" t="s">
+        <v>997</v>
+      </c>
+      <c r="B69" s="31" t="s">
         <v>998</v>
-      </c>
-      <c r="B69" s="31" t="s">
-        <v>999</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="30" t="s">
+        <v>999</v>
+      </c>
+      <c r="B70" s="31" t="s">
         <v>1000</v>
-      </c>
-      <c r="B70" s="31" t="s">
-        <v>1001</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -13576,15 +14572,15 @@
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="30" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B72" s="31" t="s">
         <v>1002</v>
-      </c>
-      <c r="B72" s="31" t="s">
-        <v>1003</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="30" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="B73" s="31" t="s">
         <v>138</v>
@@ -13592,7 +14588,7 @@
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="30" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="B74" s="31" t="s">
         <v>269</v>
@@ -13600,50 +14596,50 @@
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="30" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B75" s="31" t="s">
         <v>1006</v>
-      </c>
-      <c r="B75" s="31" t="s">
-        <v>1007</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="30" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B76" s="31" t="s">
         <v>1008</v>
-      </c>
-      <c r="B76" s="31" t="s">
-        <v>1009</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="30" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B77" s="31" t="s">
         <v>1010</v>
-      </c>
-      <c r="B77" s="31" t="s">
-        <v>1011</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="30" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B78" s="31" t="s">
         <v>1012</v>
-      </c>
-      <c r="B78" s="31" t="s">
-        <v>1013</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="30" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B79" s="31" t="s">
         <v>1014</v>
-      </c>
-      <c r="B79" s="31" t="s">
-        <v>1015</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="30" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B80" s="31" t="s">
         <v>1016</v>
-      </c>
-      <c r="B80" s="31" t="s">
-        <v>1017</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -13664,15 +14660,15 @@
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="30" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B83" s="31" t="s">
         <v>1018</v>
-      </c>
-      <c r="B83" s="31" t="s">
-        <v>1019</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="30" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="B84" s="31" t="s">
         <v>234</v>
@@ -13683,7 +14679,7 @@
         <v>178</v>
       </c>
       <c r="B85" s="31" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -13704,7 +14700,7 @@
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="30" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="B88" s="31" t="s">
         <v>237</v>
@@ -13720,18 +14716,18 @@
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="30" t="s">
+        <v>1022</v>
+      </c>
+      <c r="B90" s="31" t="s">
         <v>1023</v>
-      </c>
-      <c r="B90" s="31" t="s">
-        <v>1024</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="30" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B91" s="31" t="s">
         <v>1025</v>
-      </c>
-      <c r="B91" s="31" t="s">
-        <v>1026</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -13744,10 +14740,10 @@
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="30" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B93" s="31" t="s">
         <v>1027</v>
-      </c>
-      <c r="B93" s="31" t="s">
-        <v>1028</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -13776,15 +14772,15 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="30" t="s">
+        <v>1028</v>
+      </c>
+      <c r="B97" s="31" t="s">
         <v>1029</v>
-      </c>
-      <c r="B97" s="31" t="s">
-        <v>1030</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="30" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B98" s="31" t="s">
         <v>206</v>
@@ -13792,50 +14788,50 @@
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="30" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B99" s="31" t="s">
         <v>1032</v>
-      </c>
-      <c r="B99" s="31" t="s">
-        <v>1033</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" s="30" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B100" s="31" t="s">
         <v>1034</v>
-      </c>
-      <c r="B100" s="31" t="s">
-        <v>1035</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" s="30" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B101" s="31" t="s">
         <v>1036</v>
-      </c>
-      <c r="B101" s="31" t="s">
-        <v>1037</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="30" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B102" s="31" t="s">
         <v>1038</v>
-      </c>
-      <c r="B102" s="31" t="s">
-        <v>1039</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="30" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B103" s="31" t="s">
         <v>1040</v>
-      </c>
-      <c r="B103" s="31" t="s">
-        <v>1041</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="30" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B104" s="31" t="s">
         <v>1042</v>
-      </c>
-      <c r="B104" s="31" t="s">
-        <v>1043</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -13843,12 +14839,12 @@
         <v>164</v>
       </c>
       <c r="B105" s="31" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" s="30" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="B106" s="31" t="s">
         <v>202</v>
@@ -13856,18 +14852,18 @@
     </row>
     <row r="107" spans="1:2">
       <c r="A107" s="30" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B107" s="31" t="s">
         <v>1046</v>
-      </c>
-      <c r="B107" s="31" t="s">
-        <v>1047</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="30" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B108" s="31" t="s">
         <v>1048</v>
-      </c>
-      <c r="B108" s="31" t="s">
-        <v>1049</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -13883,15 +14879,15 @@
         <v>153</v>
       </c>
       <c r="B110" s="31" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="30" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B111" s="31" t="s">
         <v>1051</v>
-      </c>
-      <c r="B111" s="31" t="s">
-        <v>1052</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -13907,23 +14903,23 @@
         <v>186</v>
       </c>
       <c r="B113" s="31" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="30" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B114" s="31" t="s">
         <v>1054</v>
-      </c>
-      <c r="B114" s="31" t="s">
-        <v>1055</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="30" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B115" s="31" t="s">
         <v>1056</v>
-      </c>
-      <c r="B115" s="31" t="s">
-        <v>1057</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -13936,42 +14932,42 @@
     </row>
     <row r="117" spans="1:2">
       <c r="A117" s="30" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B117" s="31" t="s">
         <v>1058</v>
-      </c>
-      <c r="B117" s="31" t="s">
-        <v>1059</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" s="30" t="s">
+        <v>1059</v>
+      </c>
+      <c r="B118" s="31" t="s">
         <v>1060</v>
-      </c>
-      <c r="B118" s="31" t="s">
-        <v>1061</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" s="30" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B119" s="31" t="s">
         <v>1062</v>
-      </c>
-      <c r="B119" s="31" t="s">
-        <v>1063</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="30" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B120" s="31" t="s">
         <v>1064</v>
-      </c>
-      <c r="B120" s="31" t="s">
-        <v>1065</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" s="30" t="s">
+        <v>1065</v>
+      </c>
+      <c r="B121" s="31" t="s">
         <v>1066</v>
-      </c>
-      <c r="B121" s="31" t="s">
-        <v>1067</v>
       </c>
     </row>
   </sheetData>
@@ -13993,7 +14989,7 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1">
       <c r="A1" s="35" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>592</v>
@@ -14705,7 +15701,7 @@
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="36" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
       <c r="B90" s="34" t="s">
         <v>139</v>
@@ -14739,10 +15735,10 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1">
       <c r="A1" s="35" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -14971,226 +15967,226 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="34" t="s">
+        <v>1374</v>
+      </c>
+      <c r="B30" s="34" t="s">
         <v>1375</v>
-      </c>
-      <c r="B30" s="34" t="s">
-        <v>1376</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="34" t="s">
+        <v>1376</v>
+      </c>
+      <c r="B31" s="34" t="s">
         <v>1377</v>
-      </c>
-      <c r="B31" s="34" t="s">
-        <v>1378</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="48" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B32" s="34" t="s">
         <v>1379</v>
-      </c>
-      <c r="B32" s="34" t="s">
-        <v>1380</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="34" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B33" s="34" t="s">
         <v>1381</v>
-      </c>
-      <c r="B33" s="34" t="s">
-        <v>1382</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="34" t="s">
+        <v>1382</v>
+      </c>
+      <c r="B34" s="34" t="s">
         <v>1383</v>
-      </c>
-      <c r="B34" s="34" t="s">
-        <v>1384</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="34" t="s">
+        <v>1384</v>
+      </c>
+      <c r="B35" s="34" t="s">
         <v>1385</v>
-      </c>
-      <c r="B35" s="34" t="s">
-        <v>1386</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="34" t="s">
+        <v>1386</v>
+      </c>
+      <c r="B36" s="34" t="s">
         <v>1387</v>
-      </c>
-      <c r="B36" s="34" t="s">
-        <v>1388</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="34" t="s">
+        <v>1388</v>
+      </c>
+      <c r="B37" s="34" t="s">
         <v>1389</v>
-      </c>
-      <c r="B37" s="34" t="s">
-        <v>1390</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="48" t="s">
+        <v>1390</v>
+      </c>
+      <c r="B38" s="34" t="s">
         <v>1391</v>
-      </c>
-      <c r="B38" s="34" t="s">
-        <v>1392</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="34" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B39" s="34" t="s">
         <v>1393</v>
-      </c>
-      <c r="B39" s="34" t="s">
-        <v>1394</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="34" t="s">
+        <v>1394</v>
+      </c>
+      <c r="B40" s="34" t="s">
         <v>1395</v>
-      </c>
-      <c r="B40" s="34" t="s">
-        <v>1396</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="34" t="s">
-        <v>1398</v>
+        <v>1397</v>
       </c>
       <c r="B41" s="34" t="s">
-        <v>1397</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="34" t="s">
-        <v>1373</v>
+        <v>1372</v>
       </c>
       <c r="B42" s="34" t="s">
-        <v>1399</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="34" t="s">
-        <v>1374</v>
+        <v>1373</v>
       </c>
       <c r="B43" s="34" t="s">
-        <v>1400</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="34" t="s">
+        <v>1400</v>
+      </c>
+      <c r="B44" s="34" t="s">
         <v>1401</v>
-      </c>
-      <c r="B44" s="34" t="s">
-        <v>1402</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="34" t="s">
+        <v>1402</v>
+      </c>
+      <c r="B45" s="34" t="s">
         <v>1403</v>
-      </c>
-      <c r="B45" s="34" t="s">
-        <v>1404</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="34" t="s">
+        <v>1404</v>
+      </c>
+      <c r="B46" s="34" t="s">
         <v>1405</v>
-      </c>
-      <c r="B46" s="34" t="s">
-        <v>1406</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="34" t="s">
+        <v>1406</v>
+      </c>
+      <c r="B47" s="34" t="s">
         <v>1407</v>
-      </c>
-      <c r="B47" s="34" t="s">
-        <v>1408</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="34" t="s">
+        <v>1408</v>
+      </c>
+      <c r="B48" s="34" t="s">
         <v>1409</v>
-      </c>
-      <c r="B48" s="34" t="s">
-        <v>1410</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="34" t="s">
+        <v>1410</v>
+      </c>
+      <c r="B49" s="34" t="s">
         <v>1411</v>
-      </c>
-      <c r="B49" s="34" t="s">
-        <v>1412</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="34" t="s">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="B50" s="34" t="s">
-        <v>1547</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="34" t="s">
+        <v>1413</v>
+      </c>
+      <c r="B51" s="34" t="s">
         <v>1414</v>
-      </c>
-      <c r="B51" s="34" t="s">
-        <v>1415</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="34" t="s">
+        <v>1415</v>
+      </c>
+      <c r="B52" s="34" t="s">
         <v>1416</v>
-      </c>
-      <c r="B52" s="34" t="s">
-        <v>1417</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="34" t="s">
+        <v>1417</v>
+      </c>
+      <c r="B53" s="34" t="s">
         <v>1418</v>
-      </c>
-      <c r="B53" s="34" t="s">
-        <v>1419</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="34" t="s">
+        <v>1419</v>
+      </c>
+      <c r="B54" s="34" t="s">
         <v>1420</v>
-      </c>
-      <c r="B54" s="34" t="s">
-        <v>1421</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="34" t="s">
+        <v>1421</v>
+      </c>
+      <c r="B55" s="34" t="s">
         <v>1422</v>
-      </c>
-      <c r="B55" s="34" t="s">
-        <v>1423</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="34" t="s">
+        <v>1423</v>
+      </c>
+      <c r="B56" s="34" t="s">
         <v>1424</v>
-      </c>
-      <c r="B56" s="34" t="s">
-        <v>1425</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="34" t="s">
+        <v>1425</v>
+      </c>
+      <c r="B57" s="34" t="s">
         <v>1426</v>
-      </c>
-      <c r="B57" s="34" t="s">
-        <v>1427</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -15198,527 +16194,527 @@
         <v>230</v>
       </c>
       <c r="B58" s="34" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="34" t="s">
+        <v>1427</v>
+      </c>
+      <c r="B59" s="34" t="s">
         <v>1428</v>
-      </c>
-      <c r="B59" s="34" t="s">
-        <v>1429</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="34" t="s">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="B60" s="34" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="34" t="s">
+        <v>1430</v>
+      </c>
+      <c r="B61" s="34" t="s">
         <v>1431</v>
-      </c>
-      <c r="B61" s="34" t="s">
-        <v>1432</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="34" t="s">
+        <v>1432</v>
+      </c>
+      <c r="B62" s="34" t="s">
         <v>1433</v>
-      </c>
-      <c r="B62" s="34" t="s">
-        <v>1434</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="34" t="s">
+        <v>1434</v>
+      </c>
+      <c r="B63" s="34" t="s">
         <v>1435</v>
-      </c>
-      <c r="B63" s="34" t="s">
-        <v>1436</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="34" t="s">
+        <v>1436</v>
+      </c>
+      <c r="B64" s="34" t="s">
         <v>1437</v>
-      </c>
-      <c r="B64" s="34" t="s">
-        <v>1438</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="34" t="s">
+        <v>1438</v>
+      </c>
+      <c r="B65" s="34" t="s">
         <v>1439</v>
-      </c>
-      <c r="B65" s="34" t="s">
-        <v>1440</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="34" t="s">
+        <v>1440</v>
+      </c>
+      <c r="B66" s="34" t="s">
         <v>1441</v>
-      </c>
-      <c r="B66" s="34" t="s">
-        <v>1442</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="34" t="s">
+        <v>1442</v>
+      </c>
+      <c r="B67" s="34" t="s">
         <v>1443</v>
-      </c>
-      <c r="B67" s="34" t="s">
-        <v>1444</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="34" t="s">
+        <v>1444</v>
+      </c>
+      <c r="B68" s="34" t="s">
         <v>1445</v>
-      </c>
-      <c r="B68" s="34" t="s">
-        <v>1446</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="34" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B69" s="34" t="s">
         <v>1447</v>
-      </c>
-      <c r="B69" s="34" t="s">
-        <v>1448</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="34" t="s">
+        <v>1448</v>
+      </c>
+      <c r="B70" s="34" t="s">
         <v>1449</v>
-      </c>
-      <c r="B70" s="34" t="s">
-        <v>1450</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="34" t="s">
+        <v>1450</v>
+      </c>
+      <c r="B71" s="34" t="s">
         <v>1451</v>
-      </c>
-      <c r="B71" s="34" t="s">
-        <v>1452</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="34" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="B72" s="34" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="34" t="s">
+        <v>1453</v>
+      </c>
+      <c r="B73" s="34" t="s">
         <v>1454</v>
-      </c>
-      <c r="B73" s="34" t="s">
-        <v>1455</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="34" t="s">
+        <v>1455</v>
+      </c>
+      <c r="B74" s="34" t="s">
         <v>1456</v>
-      </c>
-      <c r="B74" s="34" t="s">
-        <v>1457</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="34" t="s">
+        <v>1457</v>
+      </c>
+      <c r="B75" s="34" t="s">
         <v>1458</v>
-      </c>
-      <c r="B75" s="34" t="s">
-        <v>1459</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="34" t="s">
+        <v>1459</v>
+      </c>
+      <c r="B76" s="34" t="s">
         <v>1460</v>
-      </c>
-      <c r="B76" s="34" t="s">
-        <v>1461</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="34" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B77" s="34" t="s">
         <v>1462</v>
-      </c>
-      <c r="B77" s="34" t="s">
-        <v>1463</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="34" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="B78" s="34" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="34" t="s">
+        <v>1464</v>
+      </c>
+      <c r="B79" s="34" t="s">
         <v>1465</v>
-      </c>
-      <c r="B79" s="34" t="s">
-        <v>1466</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="34" t="s">
+        <v>1466</v>
+      </c>
+      <c r="B80" s="34" t="s">
         <v>1467</v>
-      </c>
-      <c r="B80" s="34" t="s">
-        <v>1468</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="34" t="s">
+        <v>1468</v>
+      </c>
+      <c r="B81" s="34" t="s">
         <v>1469</v>
-      </c>
-      <c r="B81" s="34" t="s">
-        <v>1470</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="34" t="s">
+        <v>1470</v>
+      </c>
+      <c r="B82" s="34" t="s">
         <v>1471</v>
-      </c>
-      <c r="B82" s="34" t="s">
-        <v>1472</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="34" t="s">
+        <v>1472</v>
+      </c>
+      <c r="B83" s="34" t="s">
         <v>1473</v>
-      </c>
-      <c r="B83" s="34" t="s">
-        <v>1474</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="34" t="s">
+        <v>1474</v>
+      </c>
+      <c r="B84" s="34" t="s">
         <v>1475</v>
-      </c>
-      <c r="B84" s="34" t="s">
-        <v>1476</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="34" t="s">
+        <v>1476</v>
+      </c>
+      <c r="B85" s="34" t="s">
         <v>1477</v>
-      </c>
-      <c r="B85" s="34" t="s">
-        <v>1478</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="34" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="B86" s="34" t="s">
-        <v>1550</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="34" t="s">
+        <v>1479</v>
+      </c>
+      <c r="B87" s="34" t="s">
         <v>1480</v>
-      </c>
-      <c r="B87" s="34" t="s">
-        <v>1481</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="34" t="s">
+        <v>1481</v>
+      </c>
+      <c r="B88" s="34" t="s">
         <v>1482</v>
-      </c>
-      <c r="B88" s="34" t="s">
-        <v>1483</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="34" t="s">
+        <v>1483</v>
+      </c>
+      <c r="B89" s="34" t="s">
         <v>1484</v>
-      </c>
-      <c r="B89" s="34" t="s">
-        <v>1485</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="34" t="s">
-        <v>1486</v>
+        <v>1485</v>
       </c>
       <c r="B90" s="34" t="s">
-        <v>1551</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="34" t="s">
+        <v>1486</v>
+      </c>
+      <c r="B91" s="34" t="s">
         <v>1487</v>
-      </c>
-      <c r="B91" s="34" t="s">
-        <v>1488</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="34" t="s">
+        <v>1488</v>
+      </c>
+      <c r="B92" s="34" t="s">
         <v>1489</v>
-      </c>
-      <c r="B92" s="34" t="s">
-        <v>1490</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="34" t="s">
+        <v>1490</v>
+      </c>
+      <c r="B93" s="34" t="s">
         <v>1491</v>
-      </c>
-      <c r="B93" s="34" t="s">
-        <v>1492</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="34" t="s">
+        <v>1492</v>
+      </c>
+      <c r="B94" s="34" t="s">
         <v>1493</v>
-      </c>
-      <c r="B94" s="34" t="s">
-        <v>1494</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="34" t="s">
+        <v>1494</v>
+      </c>
+      <c r="B95" s="34" t="s">
         <v>1495</v>
-      </c>
-      <c r="B95" s="34" t="s">
-        <v>1496</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="34" t="s">
+        <v>1551</v>
+      </c>
+      <c r="B96" s="34" t="s">
         <v>1552</v>
-      </c>
-      <c r="B96" s="34" t="s">
-        <v>1553</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="34" t="s">
+        <v>1496</v>
+      </c>
+      <c r="B97" s="34" t="s">
         <v>1497</v>
-      </c>
-      <c r="B97" s="34" t="s">
-        <v>1498</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="34" t="s">
-        <v>1500</v>
+        <v>1499</v>
       </c>
       <c r="B98" s="34" t="s">
-        <v>1499</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="34" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="B99" s="34" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" s="34" t="s">
+        <v>1501</v>
+      </c>
+      <c r="B100" s="34" t="s">
         <v>1502</v>
-      </c>
-      <c r="B100" s="34" t="s">
-        <v>1503</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" s="34" t="s">
+        <v>1503</v>
+      </c>
+      <c r="B101" s="34" t="s">
         <v>1504</v>
-      </c>
-      <c r="B101" s="34" t="s">
-        <v>1505</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="34" t="s">
+        <v>1505</v>
+      </c>
+      <c r="B102" s="34" t="s">
         <v>1506</v>
-      </c>
-      <c r="B102" s="34" t="s">
-        <v>1507</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="34" t="s">
+        <v>1507</v>
+      </c>
+      <c r="B103" s="34" t="s">
         <v>1508</v>
-      </c>
-      <c r="B103" s="34" t="s">
-        <v>1509</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="34" t="s">
-        <v>1511</v>
+        <v>1510</v>
       </c>
       <c r="B104" s="34" t="s">
-        <v>1510</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="34" t="s">
+        <v>1511</v>
+      </c>
+      <c r="B105" s="34" t="s">
         <v>1512</v>
-      </c>
-      <c r="B105" s="34" t="s">
-        <v>1513</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" s="34" t="s">
+        <v>1513</v>
+      </c>
+      <c r="B106" s="34" t="s">
         <v>1514</v>
-      </c>
-      <c r="B106" s="34" t="s">
-        <v>1515</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" s="34" t="s">
-        <v>1372</v>
+        <v>1371</v>
       </c>
       <c r="B107" s="34" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="34" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
       <c r="B108" s="34" t="s">
-        <v>1532</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" s="34" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="B109" s="34" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" s="34" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="B110" s="34" t="s">
-        <v>1531</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="34" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="B111" s="34" t="s">
-        <v>1534</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" s="34" t="s">
-        <v>1519</v>
+        <v>1518</v>
       </c>
       <c r="B112" s="34" t="s">
-        <v>1535</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="34" t="s">
-        <v>1520</v>
+        <v>1519</v>
       </c>
       <c r="B113" s="34" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="34" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="B114" s="34" t="s">
-        <v>1537</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="34" t="s">
-        <v>1556</v>
+        <v>1555</v>
       </c>
       <c r="B115" s="34" t="s">
-        <v>1538</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" s="34" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="B116" s="34" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" s="34" t="s">
-        <v>1523</v>
+        <v>1522</v>
       </c>
       <c r="B117" s="34" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" s="34" t="s">
-        <v>1524</v>
+        <v>1523</v>
       </c>
       <c r="B118" s="34" t="s">
-        <v>1541</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" s="34" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="B119" s="34" t="s">
-        <v>1542</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="34" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="B120" s="34" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" s="34" t="s">
-        <v>1527</v>
+        <v>1526</v>
       </c>
       <c r="B121" s="34" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" s="34" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="B122" s="34" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" s="34" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="B123" s="34" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -16134,162 +17130,162 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="40" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="B2" s="38" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="40" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="B3" s="38" t="s">
-        <v>1344</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="40" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
       <c r="B4" s="38" t="s">
-        <v>1345</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="40" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="B5" s="38" t="s">
-        <v>1346</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="40" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="B6" s="38" t="s">
-        <v>1347</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="40" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
       <c r="B7" s="38" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="40" t="s">
-        <v>1329</v>
+        <v>1328</v>
       </c>
       <c r="B8" s="38" t="s">
-        <v>1349</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="40" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="B9" s="38" t="s">
-        <v>1350</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="40" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="B10" s="38" t="s">
-        <v>1351</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="40" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="B11" s="38" t="s">
-        <v>1352</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="40" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="B12" s="38" t="s">
-        <v>1353</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="40" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="40" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>1355</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="40" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="B15" s="38" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="40" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="40" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="B17" s="38" t="s">
-        <v>1358</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="40" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>1359</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="40" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="B19" s="38" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="40" t="s">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="B20" s="38" t="s">
-        <v>1361</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="40" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="B21" s="38" t="s">
-        <v>1362</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="63" spans="2:2">

--- a/question_bank/ENGLISH.xlsx
+++ b/question_bank/ENGLISH.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7500" firstSheet="16" activeTab="19"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7500" firstSheet="17" activeTab="20"/>
   </bookViews>
   <sheets>
     <sheet name="Index" sheetId="14" r:id="rId1"/>
@@ -32,11 +32,13 @@
     <sheet name="Correct Sentences" sheetId="15" r:id="rId18"/>
     <sheet name="Jumble Words" sheetId="13" r:id="rId19"/>
     <sheet name="Comparison of Adjectives" sheetId="23" r:id="rId20"/>
+    <sheet name="Formation of Adjectives" sheetId="25" r:id="rId21"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'Comparison of Adjectives'!$A$1:$B$70</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Direct - Indirect 1'!$A$1:$B$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Direct - Indirect 2'!$A$1:$B$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'Formation of Adjectives'!$A$1:$B$85</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -48,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1818" uniqueCount="1747">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1989" uniqueCount="1905">
   <si>
     <t>Amazing</t>
   </si>
@@ -5125,6 +5127,9 @@
   </si>
   <si>
     <t>Adverb</t>
+  </si>
+  <si>
+    <t>Adjective</t>
   </si>
   <si>
     <t>Jumple Words</t>
@@ -8602,6 +8607,405 @@
     <t>An assembly of listeners</t>
   </si>
   <si>
+    <t>beneficial</t>
+  </si>
+  <si>
+    <t>Child</t>
+  </si>
+  <si>
+    <t>childish</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>educational</t>
+  </si>
+  <si>
+    <t>foolish</t>
+  </si>
+  <si>
+    <t>devotional</t>
+  </si>
+  <si>
+    <t>Beauty</t>
+  </si>
+  <si>
+    <t>beautiful</t>
+  </si>
+  <si>
+    <t>Health</t>
+  </si>
+  <si>
+    <t>healthy</t>
+  </si>
+  <si>
+    <t>Care</t>
+  </si>
+  <si>
+    <t>careful</t>
+  </si>
+  <si>
+    <t>Dirt</t>
+  </si>
+  <si>
+    <t>dirty</t>
+  </si>
+  <si>
+    <t>hopeful</t>
+  </si>
+  <si>
+    <t>Ease</t>
+  </si>
+  <si>
+    <t>needful</t>
+  </si>
+  <si>
+    <t>Storm</t>
+  </si>
+  <si>
+    <t>stormy</t>
+  </si>
+  <si>
+    <t>peaceful</t>
+  </si>
+  <si>
+    <t>sunny</t>
+  </si>
+  <si>
+    <t>playful</t>
+  </si>
+  <si>
+    <t>Leaf</t>
+  </si>
+  <si>
+    <t>leafy</t>
+  </si>
+  <si>
+    <t>successful</t>
+  </si>
+  <si>
+    <t>angry</t>
+  </si>
+  <si>
+    <t>useful</t>
+  </si>
+  <si>
+    <t>Glory</t>
+  </si>
+  <si>
+    <t>glorious</t>
+  </si>
+  <si>
+    <t>Wonder</t>
+  </si>
+  <si>
+    <t>wonderful</t>
+  </si>
+  <si>
+    <t>Envy</t>
+  </si>
+  <si>
+    <t>envious</t>
+  </si>
+  <si>
+    <t>Shame</t>
+  </si>
+  <si>
+    <t>shameless</t>
+  </si>
+  <si>
+    <t>Ambition</t>
+  </si>
+  <si>
+    <t>ambitious</t>
+  </si>
+  <si>
+    <t>Sense</t>
+  </si>
+  <si>
+    <t>senseless</t>
+  </si>
+  <si>
+    <t>Courage</t>
+  </si>
+  <si>
+    <t>courageous</t>
+  </si>
+  <si>
+    <t>Outrage</t>
+  </si>
+  <si>
+    <t>outrageous</t>
+  </si>
+  <si>
+    <t>Danger</t>
+  </si>
+  <si>
+    <t>dangerous</t>
+  </si>
+  <si>
+    <t>Silk</t>
+  </si>
+  <si>
+    <t>silken</t>
+  </si>
+  <si>
+    <t>Nerve</t>
+  </si>
+  <si>
+    <t>nervous</t>
+  </si>
+  <si>
+    <t>Gold</t>
+  </si>
+  <si>
+    <t>golden</t>
+  </si>
+  <si>
+    <t>telegraphic</t>
+  </si>
+  <si>
+    <t>Cost</t>
+  </si>
+  <si>
+    <t>costly</t>
+  </si>
+  <si>
+    <t>manly</t>
+  </si>
+  <si>
+    <t>Belief</t>
+  </si>
+  <si>
+    <t>believable</t>
+  </si>
+  <si>
+    <t>King</t>
+  </si>
+  <si>
+    <t>kingly</t>
+  </si>
+  <si>
+    <t>Desire</t>
+  </si>
+  <si>
+    <t>desirable</t>
+  </si>
+  <si>
+    <t>Pardon</t>
+  </si>
+  <si>
+    <t>Pardonable</t>
+  </si>
+  <si>
+    <t>Music</t>
+  </si>
+  <si>
+    <t>musical</t>
+  </si>
+  <si>
+    <t>Office</t>
+  </si>
+  <si>
+    <t>official</t>
+  </si>
+  <si>
+    <t>Crime</t>
+  </si>
+  <si>
+    <t>criminal</t>
+  </si>
+  <si>
+    <t>Voice</t>
+  </si>
+  <si>
+    <t>Attraction</t>
+  </si>
+  <si>
+    <t>attractive</t>
+  </si>
+  <si>
+    <t>People</t>
+  </si>
+  <si>
+    <t>Destruction</t>
+  </si>
+  <si>
+    <t>destructive</t>
+  </si>
+  <si>
+    <t>Hand</t>
+  </si>
+  <si>
+    <t>Distribution</t>
+  </si>
+  <si>
+    <t>distributive</t>
+  </si>
+  <si>
+    <t>Production</t>
+  </si>
+  <si>
+    <t>productive</t>
+  </si>
+  <si>
+    <t>Quarrel</t>
+  </si>
+  <si>
+    <t>vocal</t>
+  </si>
+  <si>
+    <t>popular</t>
+  </si>
+  <si>
+    <t>handsome</t>
+  </si>
+  <si>
+    <t>troublesome</t>
+  </si>
+  <si>
+    <t>quarrelsome</t>
+  </si>
+  <si>
+    <t>Act</t>
+  </si>
+  <si>
+    <t>active</t>
+  </si>
+  <si>
+    <t>movable</t>
+  </si>
+  <si>
+    <t>Attract</t>
+  </si>
+  <si>
+    <t>Rely</t>
+  </si>
+  <si>
+    <t>reliable</t>
+  </si>
+  <si>
+    <t>Detect</t>
+  </si>
+  <si>
+    <t>detective</t>
+  </si>
+  <si>
+    <t>Add</t>
+  </si>
+  <si>
+    <t>Deceive</t>
+  </si>
+  <si>
+    <t>deceptive</t>
+  </si>
+  <si>
+    <t>Edit</t>
+  </si>
+  <si>
+    <t>additional</t>
+  </si>
+  <si>
+    <t>editorial</t>
+  </si>
+  <si>
+    <t>inclusive</t>
+  </si>
+  <si>
+    <t>forgetful</t>
+  </si>
+  <si>
+    <t>Instruct</t>
+  </si>
+  <si>
+    <t>instructive</t>
+  </si>
+  <si>
+    <t>Trust</t>
+  </si>
+  <si>
+    <t>Talk</t>
+  </si>
+  <si>
+    <t>talkative</t>
+  </si>
+  <si>
+    <t>Invent</t>
+  </si>
+  <si>
+    <t>Agree</t>
+  </si>
+  <si>
+    <t>agreeable</t>
+  </si>
+  <si>
+    <t>Prevent</t>
+  </si>
+  <si>
+    <t>preventive</t>
+  </si>
+  <si>
+    <t>Advise</t>
+  </si>
+  <si>
+    <t>advisory</t>
+  </si>
+  <si>
+    <t>enjoyable</t>
+  </si>
+  <si>
+    <t>lovely</t>
+  </si>
+  <si>
+    <t>Economic</t>
+  </si>
+  <si>
+    <t>economical</t>
+  </si>
+  <si>
+    <t>Black</t>
+  </si>
+  <si>
+    <t>blackish</t>
+  </si>
+  <si>
+    <t>Tragic</t>
+  </si>
+  <si>
+    <t>tragical</t>
+  </si>
+  <si>
+    <t>White</t>
+  </si>
+  <si>
+    <t>whitish</t>
+  </si>
+  <si>
+    <t>Three</t>
+  </si>
+  <si>
+    <t>threefold</t>
+  </si>
+  <si>
+    <t>Large</t>
+  </si>
+  <si>
+    <t>largely</t>
+  </si>
+  <si>
+    <t>Whole</t>
+  </si>
+  <si>
+    <t>wholesome</t>
+  </si>
+  <si>
+    <t>Sick</t>
+  </si>
+  <si>
+    <t>sickly</t>
+  </si>
+  <si>
     <t>Positive</t>
   </si>
   <si>
@@ -9016,7 +9420,79 @@
     <t>more industrious | most industrious</t>
   </si>
   <si>
-    <t>more learned | most learned may</t>
+    <t>more learned | most learned</t>
+  </si>
+  <si>
+    <t>inventive</t>
+  </si>
+  <si>
+    <t>Boy</t>
+  </si>
+  <si>
+    <t>boyish</t>
+  </si>
+  <si>
+    <t>Benefit</t>
+  </si>
+  <si>
+    <t>Fool</t>
+  </si>
+  <si>
+    <t>Devotion</t>
+  </si>
+  <si>
+    <t>easy</t>
+  </si>
+  <si>
+    <t>Sun</t>
+  </si>
+  <si>
+    <t>Play</t>
+  </si>
+  <si>
+    <t>Success</t>
+  </si>
+  <si>
+    <t>Use</t>
+  </si>
+  <si>
+    <t>ceaseless</t>
+  </si>
+  <si>
+    <t>Life</t>
+  </si>
+  <si>
+    <t>lively (লাইভলি)</t>
+  </si>
+  <si>
+    <t>miserly (কৃপণ)</t>
+  </si>
+  <si>
+    <t>Telegraph Laugh (হাসি)</t>
+  </si>
+  <si>
+    <t>laughable</t>
+  </si>
+  <si>
+    <t>Need</t>
+  </si>
+  <si>
+    <t>peace</t>
+  </si>
+  <si>
+    <t>Laugh</t>
+  </si>
+  <si>
+    <t>Man</t>
+  </si>
+  <si>
+    <t>trustful</t>
+  </si>
+  <si>
+    <t>Noun / Verb / Adjective</t>
+  </si>
+  <si>
+    <t>Formation of Adjectives</t>
   </si>
 </sst>
 </file>
@@ -9222,7 +9698,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -9327,6 +9803,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -9608,7 +10085,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:B30"/>
+  <dimension ref="B2:B31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="34.7109375" bestFit="1" customWidth="1"/>
@@ -9616,7 +10093,7 @@
   <sheetData>
     <row r="2" spans="2:2">
       <c r="B2" s="1" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
     </row>
     <row r="3" spans="2:2">
@@ -9644,7 +10121,7 @@
     </row>
     <row r="8" spans="2:2" s="2" customFormat="1">
       <c r="B8" s="1" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
     </row>
     <row r="9" spans="2:2">
@@ -9674,7 +10151,7 @@
     </row>
     <row r="14" spans="2:2">
       <c r="B14" s="7" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="16" spans="2:2">
@@ -9684,7 +10161,7 @@
     </row>
     <row r="17" spans="2:2">
       <c r="B17" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
     </row>
     <row r="18" spans="2:2">
@@ -9699,7 +10176,7 @@
     </row>
     <row r="20" spans="2:2">
       <c r="B20" s="7" t="s">
-        <v>1225</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="21" spans="2:2">
@@ -9719,33 +10196,38 @@
     </row>
     <row r="24" spans="2:2">
       <c r="B24" s="7" t="s">
-        <v>1677</v>
+        <v>1811</v>
       </c>
     </row>
     <row r="25" spans="2:2">
-      <c r="B25" t="s">
+      <c r="B25" s="7" t="s">
+        <v>1904</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2">
+      <c r="B26" t="s">
         <v>596</v>
-      </c>
-    </row>
-    <row r="28" spans="2:2">
-      <c r="B28" s="7" t="s">
-        <v>595</v>
       </c>
     </row>
     <row r="29" spans="2:2">
       <c r="B29" s="7" t="s">
-        <v>664</v>
+        <v>595</v>
       </c>
     </row>
     <row r="30" spans="2:2">
       <c r="B30" s="7" t="s">
-        <v>916</v>
+        <v>664</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2">
+      <c r="B31" s="7" t="s">
+        <v>917</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B28" location="'Correct Spelling'!A1" display="Correct Spelling"/>
-    <hyperlink ref="B29" location="'Correct Sentences'!A1" display="Correct Sentences"/>
+    <hyperlink ref="B29" location="'Correct Spelling'!A1" display="Correct Spelling"/>
+    <hyperlink ref="B30" location="'Correct Sentences'!A1" display="Correct Sentences"/>
     <hyperlink ref="B3" location="'One Word Subs'!A1" display="One Word Substitution"/>
     <hyperlink ref="B4" location="'One Word Subs (MS)'!A1" display="One Word Substitution (MS)"/>
     <hyperlink ref="B5" location="Antonyms!A1" display="Antonyms"/>
@@ -9754,13 +10236,14 @@
     <hyperlink ref="B10" location="'Direct - Indirect 2'!A1" display="Direct - Indirec 1"/>
     <hyperlink ref="B11" location="'Direct-Indirect 3'!A1" display="Direct - Indirec 1"/>
     <hyperlink ref="B12" location="'Voice Change'!A1" display="Voice Change"/>
-    <hyperlink ref="B30" location="'Jumble Words'!A1" display="Jumple Words"/>
+    <hyperlink ref="B31" location="'Jumble Words'!A1" display="Jumple Words"/>
     <hyperlink ref="B13" location="'Positive-Negative'!A1" display="Positive-Negative"/>
     <hyperlink ref="B14" location="'Transformation of Sentences'!A1" display="Transformation of Sentences (Mixed)"/>
     <hyperlink ref="B20" location="Article!A1" display="Article"/>
     <hyperlink ref="B21" location="Preposition!A1" display="Preposition"/>
     <hyperlink ref="B18" location="'Convert to Abstarct Noun'!A1" display="Noun"/>
     <hyperlink ref="B24" location="'Comparison of Adjectives'!A1" display="Comparison of Adjectives"/>
+    <hyperlink ref="B25" location="'Formation of Adjectives'!A1" display="Formation of Adjectives"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -10494,138 +10977,138 @@
     </row>
     <row r="2" spans="1:2" ht="15.75">
       <c r="A2" s="8" t="s">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15.75">
       <c r="A3" s="8" t="s">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15.75">
       <c r="A4" s="8" t="s">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15.75">
       <c r="A5" s="8" t="s">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="15.75">
       <c r="A6" s="8" t="s">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="15.75">
       <c r="A7" s="8" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="15.75">
       <c r="A8" s="8" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="15.75">
       <c r="A9" s="8" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="15.75">
       <c r="A10" s="8" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="15.75">
       <c r="A11" s="8" t="s">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="15.75">
       <c r="A12" s="8" t="s">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="15.75">
       <c r="A13" s="8" t="s">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="15.75">
       <c r="A14" s="8" t="s">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="15.75">
       <c r="A15" s="8" t="s">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="15.75">
       <c r="A16" s="8" t="s">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="15.75">
       <c r="A17" s="8" t="s">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="8" t="s">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="B18" s="22" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
     </row>
   </sheetData>
@@ -10655,226 +11138,226 @@
     </row>
     <row r="2" spans="1:2" ht="15.75">
       <c r="A2" s="8" t="s">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15.75">
       <c r="A3" s="8" t="s">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15.75">
       <c r="A4" s="8" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15.75">
       <c r="A5" s="8" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="15.75">
       <c r="A6" s="8" t="s">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="15.75">
       <c r="A7" s="8" t="s">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="15.75">
       <c r="A8" s="8" t="s">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="15.75">
       <c r="A9" s="8" t="s">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="15.75">
       <c r="A10" s="8" t="s">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="15.75">
       <c r="A11" s="8" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="15.75">
       <c r="A12" s="8" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="15.75">
       <c r="A13" s="8" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="15.75">
       <c r="A14" s="8" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="15.75">
       <c r="A15" s="8" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="15.75">
       <c r="A16" s="8" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="15.75">
       <c r="A17" s="8" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="15.75">
       <c r="A18" s="8" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="15.75">
       <c r="A19" s="8" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="15.75">
       <c r="A20" s="8" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="15.75">
       <c r="A21" s="8" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="15.75">
       <c r="A22" s="8" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="15.75">
       <c r="A23" s="8" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="15.75">
       <c r="A24" s="8" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="15.75">
       <c r="A25" s="8" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="15.75">
       <c r="A26" s="8" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="15.75">
       <c r="A27" s="8" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="15.75">
       <c r="A28" s="8" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="15.75">
       <c r="A29" s="8" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
     </row>
   </sheetData>
@@ -10923,658 +11406,658 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="45" t="s">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="B2" s="45" t="s">
-        <v>1139</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="45" t="s">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="B3" s="45" t="s">
-        <v>1141</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="45" t="s">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="B4" s="45" t="s">
-        <v>1143</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="45" t="s">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="B5" s="45" t="s">
-        <v>1145</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="45" t="s">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="B6" s="45" t="s">
-        <v>1147</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="45" t="s">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B7" s="45" t="s">
-        <v>1149</v>
+        <v>1150</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="45" t="s">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B8" s="45" t="s">
-        <v>1151</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="45" t="s">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="B9" s="45" t="s">
-        <v>1153</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="45" t="s">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="B10" s="45" t="s">
-        <v>1155</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="45" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="B11" s="45" t="s">
-        <v>1157</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="45" t="s">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="B12" s="45" t="s">
-        <v>1159</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="15.75" thickBot="1">
       <c r="A13" s="46" t="s">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="B13" s="46" t="s">
-        <v>1161</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="45" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="B14" s="45" t="s">
-        <v>1162</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="45" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="B15" s="45" t="s">
-        <v>1163</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="45" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="B16" s="45" t="s">
-        <v>1164</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="45" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="B17" s="45" t="s">
-        <v>1165</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="45" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="B18" s="45" t="s">
-        <v>1166</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="45" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="B19" s="45" t="s">
-        <v>1167</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="45" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="B20" s="45" t="s">
-        <v>1168</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="45" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="B21" s="45" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="45" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="B22" s="45" t="s">
-        <v>1170</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="45" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="B23" s="45" t="s">
-        <v>1171</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="45" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="B24" s="45" t="s">
-        <v>1172</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="45" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="B25" s="45" t="s">
-        <v>1173</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="45" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="B26" s="45" t="s">
-        <v>1174</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="45" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="B27" s="45" t="s">
-        <v>1175</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="45" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="B28" s="45" t="s">
-        <v>1176</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="45" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="B29" s="45" t="s">
-        <v>1177</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="45" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="B30" s="45" t="s">
-        <v>1178</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="45" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="B31" s="45" t="s">
-        <v>1179</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="45" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="B32" s="45" t="s">
-        <v>1180</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="45" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="B33" s="45" t="s">
-        <v>1181</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="45" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="B34" s="45" t="s">
-        <v>1182</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="45" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="B35" s="45" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="45" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="B36" s="45" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="45" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="B37" s="45" t="s">
-        <v>1183</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="45" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="B38" s="45" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="45" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="B39" s="45" t="s">
-        <v>1185</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="45" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="B40" s="45" t="s">
-        <v>1186</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="45" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="B41" s="45" t="s">
-        <v>1187</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="45" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="B42" s="45" t="s">
-        <v>1188</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="45" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="B43" s="45" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="45" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="B44" s="45" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="45" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="B45" s="45" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="45" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="B46" s="45" t="s">
-        <v>1191</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="45" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="B47" s="45" t="s">
-        <v>1192</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="45" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="B48" s="45" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="45" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="B49" s="45" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="45" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="B50" s="45" t="s">
-        <v>1193</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="45" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="B51" s="45" t="s">
-        <v>1194</v>
+        <v>1195</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="45" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="B52" s="45" t="s">
-        <v>1195</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="45" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="B53" s="45" t="s">
-        <v>1196</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="45" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="B54" s="47" t="s">
-        <v>1197</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="45" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B55" s="47" t="s">
-        <v>1198</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="45" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="B56" s="47" t="s">
-        <v>1199</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="45" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="B57" s="47" t="s">
-        <v>1200</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="45" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="B58" s="47" t="s">
-        <v>1201</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="45" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="B59" s="47" t="s">
-        <v>1202</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="45" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="B60" s="47" t="s">
-        <v>1203</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="45" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="B61" s="47" t="s">
-        <v>1204</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="45" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="B62" s="47" t="s">
-        <v>1205</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="45" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="B63" s="47" t="s">
-        <v>1206</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="45" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="B64" s="47" t="s">
-        <v>1207</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="45" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="B65" s="47" t="s">
-        <v>1208</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="45" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="B66" s="47" t="s">
-        <v>1209</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="45" t="s">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="B67" s="47" t="s">
-        <v>1210</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="45" t="s">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="B68" s="43" t="s">
-        <v>1211</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="45" t="s">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="B69" s="45" t="s">
-        <v>1212</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="45" t="s">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="B70" s="45" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="45" t="s">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="B71" s="45" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="45" t="s">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="B72" s="45" t="s">
-        <v>1214</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="45" t="s">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="B73" s="45" t="s">
-        <v>1215</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="45" t="s">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="B74" s="45" t="s">
-        <v>1216</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="45" t="s">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="B75" s="45" t="s">
-        <v>1217</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="45" t="s">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="B76" s="45" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="45" t="s">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="B77" s="45" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="45" t="s">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="B78" s="45" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="45" t="s">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="B79" s="45" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="45" t="s">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="B80" s="45" t="s">
-        <v>1221</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="45" t="s">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="B81" s="45" t="s">
-        <v>1222</v>
+        <v>1223</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="45" t="s">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="B82" s="45" t="s">
-        <v>1223</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="45" t="s">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="B83" s="44" t="s">
-        <v>1224</v>
+        <v>1225</v>
       </c>
     </row>
   </sheetData>
@@ -12665,322 +13148,322 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1">
       <c r="A1" s="10" t="s">
-        <v>1608</v>
+        <v>1742</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1678</v>
+        <v>1812</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="33" t="s">
-        <v>1609</v>
+        <v>1743</v>
       </c>
       <c r="B2" s="33" t="s">
-        <v>1679</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="33" t="s">
-        <v>1610</v>
+        <v>1744</v>
       </c>
       <c r="B3" s="33" t="s">
-        <v>1680</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="33" t="s">
-        <v>1676</v>
+        <v>1810</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>1681</v>
+        <v>1815</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="33" t="s">
-        <v>1611</v>
+        <v>1745</v>
       </c>
       <c r="B5" s="33" t="s">
-        <v>1682</v>
+        <v>1816</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="33" t="s">
-        <v>1612</v>
+        <v>1746</v>
       </c>
       <c r="B6" s="33" t="s">
-        <v>1683</v>
+        <v>1817</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="33" t="s">
-        <v>1613</v>
+        <v>1747</v>
       </c>
       <c r="B7" s="33" t="s">
-        <v>1684</v>
+        <v>1818</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="33" t="s">
-        <v>1614</v>
+        <v>1748</v>
       </c>
       <c r="B8" s="33" t="s">
-        <v>1685</v>
+        <v>1819</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="33" t="s">
-        <v>1615</v>
+        <v>1749</v>
       </c>
       <c r="B9" s="33" t="s">
-        <v>1686</v>
+        <v>1820</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="33" t="s">
-        <v>1616</v>
+        <v>1750</v>
       </c>
       <c r="B10" s="33" t="s">
-        <v>1687</v>
+        <v>1821</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="33" t="s">
-        <v>1617</v>
+        <v>1751</v>
       </c>
       <c r="B11" s="33" t="s">
-        <v>1688</v>
+        <v>1822</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="33" t="s">
-        <v>1618</v>
+        <v>1752</v>
       </c>
       <c r="B12" s="33" t="s">
-        <v>1689</v>
+        <v>1823</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="33" t="s">
-        <v>1619</v>
+        <v>1753</v>
       </c>
       <c r="B13" s="33" t="s">
-        <v>1690</v>
+        <v>1824</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="33" t="s">
-        <v>1620</v>
+        <v>1754</v>
       </c>
       <c r="B14" s="33" t="s">
-        <v>1691</v>
+        <v>1825</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="33" t="s">
-        <v>1621</v>
+        <v>1755</v>
       </c>
       <c r="B15" s="33" t="s">
-        <v>1692</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="33" t="s">
-        <v>1622</v>
+        <v>1756</v>
       </c>
       <c r="B16" s="33" t="s">
-        <v>1693</v>
+        <v>1827</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="33" t="s">
-        <v>1623</v>
+        <v>1757</v>
       </c>
       <c r="B17" s="33" t="s">
-        <v>1694</v>
+        <v>1828</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="33" t="s">
-        <v>1624</v>
+        <v>1758</v>
       </c>
       <c r="B18" s="33" t="s">
-        <v>1695</v>
+        <v>1829</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="33" t="s">
-        <v>1625</v>
+        <v>1759</v>
       </c>
       <c r="B19" s="33" t="s">
-        <v>1696</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="33" t="s">
-        <v>1626</v>
+        <v>1760</v>
       </c>
       <c r="B20" s="33" t="s">
-        <v>1697</v>
+        <v>1831</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="33" t="s">
-        <v>1627</v>
+        <v>1761</v>
       </c>
       <c r="B21" s="33" t="s">
-        <v>1698</v>
+        <v>1832</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="33" t="s">
-        <v>1628</v>
+        <v>1762</v>
       </c>
       <c r="B22" s="33" t="s">
-        <v>1699</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="33" t="s">
-        <v>1629</v>
+        <v>1763</v>
       </c>
       <c r="B23" s="33" t="s">
-        <v>1700</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="33" t="s">
-        <v>1630</v>
+        <v>1764</v>
       </c>
       <c r="B24" s="33" t="s">
-        <v>1701</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="33" t="s">
-        <v>1631</v>
+        <v>1765</v>
       </c>
       <c r="B25" s="33" t="s">
-        <v>1702</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="33" t="s">
-        <v>1632</v>
+        <v>1766</v>
       </c>
       <c r="B26" s="33" t="s">
-        <v>1703</v>
+        <v>1837</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="33" t="s">
-        <v>1633</v>
+        <v>1767</v>
       </c>
       <c r="B27" s="33" t="s">
-        <v>1704</v>
+        <v>1838</v>
       </c>
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="33" t="s">
-        <v>1634</v>
+        <v>1768</v>
       </c>
       <c r="B28" s="33" t="s">
-        <v>1705</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="33" t="s">
-        <v>1635</v>
+        <v>1769</v>
       </c>
       <c r="B29" s="33" t="s">
-        <v>1706</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="33" t="s">
-        <v>1636</v>
+        <v>1770</v>
       </c>
       <c r="B30" s="33" t="s">
-        <v>1707</v>
+        <v>1841</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="33" t="s">
-        <v>1637</v>
+        <v>1771</v>
       </c>
       <c r="B31" s="33" t="s">
-        <v>1708</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="33" t="s">
-        <v>1638</v>
+        <v>1772</v>
       </c>
       <c r="B32" s="33" t="s">
-        <v>1709</v>
+        <v>1843</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="33" t="s">
-        <v>1639</v>
+        <v>1773</v>
       </c>
       <c r="B33" s="33" t="s">
-        <v>1710</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="33" t="s">
-        <v>1640</v>
+        <v>1774</v>
       </c>
       <c r="B34" s="33" t="s">
-        <v>1711</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="33" t="s">
-        <v>1641</v>
+        <v>1775</v>
       </c>
       <c r="B35" s="33" t="s">
-        <v>1712</v>
+        <v>1846</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="33" t="s">
-        <v>1642</v>
+        <v>1776</v>
       </c>
       <c r="B36" s="33" t="s">
-        <v>1713</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="33" t="s">
-        <v>1643</v>
+        <v>1777</v>
       </c>
       <c r="B37" s="33" t="s">
-        <v>1714</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="33" t="s">
-        <v>1644</v>
+        <v>1778</v>
       </c>
       <c r="B38" s="33" t="s">
-        <v>1715</v>
+        <v>1849</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="33" t="s">
-        <v>1645</v>
+        <v>1779</v>
       </c>
       <c r="B39" s="33" t="s">
-        <v>1716</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="33" t="s">
-        <v>1646</v>
+        <v>1780</v>
       </c>
       <c r="B40" s="33" t="s">
-        <v>1717</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="41" spans="1:2">
@@ -12988,245 +13471,943 @@
         <v>250</v>
       </c>
       <c r="B41" s="33" t="s">
-        <v>1718</v>
+        <v>1852</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="33" t="s">
-        <v>1647</v>
+        <v>1781</v>
       </c>
       <c r="B42" s="33" t="s">
-        <v>1719</v>
+        <v>1853</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="33" t="s">
-        <v>1648</v>
+        <v>1782</v>
       </c>
       <c r="B43" s="33" t="s">
-        <v>1720</v>
+        <v>1854</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="33" t="s">
-        <v>1649</v>
+        <v>1783</v>
       </c>
       <c r="B44" s="33" t="s">
-        <v>1721</v>
+        <v>1855</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="33" t="s">
-        <v>1650</v>
+        <v>1784</v>
       </c>
       <c r="B45" s="33" t="s">
-        <v>1722</v>
+        <v>1856</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="33" t="s">
-        <v>1651</v>
+        <v>1785</v>
       </c>
       <c r="B46" s="33" t="s">
-        <v>1723</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="33" t="s">
-        <v>1652</v>
+        <v>1786</v>
       </c>
       <c r="B47" s="33" t="s">
-        <v>1724</v>
+        <v>1858</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="33" t="s">
-        <v>1653</v>
+        <v>1787</v>
       </c>
       <c r="B48" s="33" t="s">
-        <v>1725</v>
+        <v>1859</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="33" t="s">
-        <v>1654</v>
+        <v>1788</v>
       </c>
       <c r="B49" s="33" t="s">
-        <v>1726</v>
+        <v>1860</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="33" t="s">
-        <v>1655</v>
+        <v>1789</v>
       </c>
       <c r="B50" s="33" t="s">
-        <v>1727</v>
+        <v>1861</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="33" t="s">
-        <v>1656</v>
+        <v>1790</v>
       </c>
       <c r="B51" s="33" t="s">
-        <v>1728</v>
+        <v>1862</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="33" t="s">
-        <v>1657</v>
+        <v>1791</v>
       </c>
       <c r="B52" s="33" t="s">
-        <v>1729</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="33" t="s">
-        <v>1658</v>
+        <v>1792</v>
       </c>
       <c r="B53" s="33" t="s">
-        <v>1730</v>
+        <v>1864</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="33" t="s">
-        <v>1659</v>
+        <v>1793</v>
       </c>
       <c r="B54" s="33" t="s">
-        <v>1731</v>
+        <v>1865</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="33" t="s">
-        <v>1660</v>
+        <v>1794</v>
       </c>
       <c r="B55" s="33" t="s">
-        <v>1732</v>
+        <v>1866</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="33" t="s">
-        <v>1661</v>
+        <v>1795</v>
       </c>
       <c r="B56" s="33" t="s">
-        <v>1733</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="33" t="s">
-        <v>1662</v>
+        <v>1796</v>
       </c>
       <c r="B57" s="33" t="s">
-        <v>1734</v>
+        <v>1868</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="33" t="s">
-        <v>1663</v>
+        <v>1797</v>
       </c>
       <c r="B58" s="33" t="s">
-        <v>1735</v>
+        <v>1869</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="33" t="s">
-        <v>1664</v>
+        <v>1798</v>
       </c>
       <c r="B59" s="33" t="s">
-        <v>1736</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="33" t="s">
-        <v>1665</v>
+        <v>1799</v>
       </c>
       <c r="B60" s="33" t="s">
-        <v>1736</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="33" t="s">
-        <v>1671</v>
+        <v>1805</v>
       </c>
       <c r="B61" s="33" t="s">
-        <v>1737</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="33" t="s">
-        <v>1672</v>
+        <v>1806</v>
       </c>
       <c r="B62" s="33" t="s">
-        <v>1738</v>
+        <v>1872</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="33" t="s">
-        <v>1675</v>
+        <v>1809</v>
       </c>
       <c r="B63" s="33" t="s">
-        <v>1739</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="33" t="s">
-        <v>1673</v>
+        <v>1807</v>
       </c>
       <c r="B64" s="33" t="s">
-        <v>1740</v>
+        <v>1874</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="33" t="s">
-        <v>1674</v>
+        <v>1808</v>
       </c>
       <c r="B65" s="33" t="s">
-        <v>1741</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="33" t="s">
-        <v>1666</v>
+        <v>1800</v>
       </c>
       <c r="B66" s="33" t="s">
-        <v>1742</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="33" t="s">
-        <v>1667</v>
+        <v>1801</v>
       </c>
       <c r="B67" s="33" t="s">
-        <v>1743</v>
+        <v>1877</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="33" t="s">
-        <v>1668</v>
+        <v>1802</v>
       </c>
       <c r="B68" s="33" t="s">
-        <v>1744</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="33" t="s">
-        <v>1669</v>
+        <v>1803</v>
       </c>
       <c r="B69" s="33" t="s">
-        <v>1745</v>
+        <v>1879</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="33" t="s">
-        <v>1670</v>
+        <v>1804</v>
       </c>
       <c r="B70" s="33" t="s">
-        <v>1746</v>
+        <v>1880</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:B70"/>
   <hyperlinks>
     <hyperlink ref="A1" location="Index!A1" display="Positive"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B85"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="24.7109375" style="52" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.140625" style="52" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.140625" style="52"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="1" customFormat="1">
+      <c r="A1" s="10" t="s">
+        <v>1903</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="52" t="s">
+        <v>1882</v>
+      </c>
+      <c r="B2" s="52" t="s">
+        <v>1883</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="52" t="s">
+        <v>1884</v>
+      </c>
+      <c r="B3" s="52" t="s">
+        <v>1609</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="52" t="s">
+        <v>1610</v>
+      </c>
+      <c r="B4" s="52" t="s">
+        <v>1611</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="52" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B5" s="52" t="s">
+        <v>1613</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="52" t="s">
+        <v>1885</v>
+      </c>
+      <c r="B6" s="52" t="s">
+        <v>1614</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="52" t="s">
+        <v>1886</v>
+      </c>
+      <c r="B7" s="52" t="s">
+        <v>1615</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="52" t="s">
+        <v>1616</v>
+      </c>
+      <c r="B8" s="52" t="s">
+        <v>1617</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="52" t="s">
+        <v>1618</v>
+      </c>
+      <c r="B9" s="52" t="s">
+        <v>1619</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="52" t="s">
+        <v>1620</v>
+      </c>
+      <c r="B10" s="52" t="s">
+        <v>1621</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="52" t="s">
+        <v>1622</v>
+      </c>
+      <c r="B11" s="52" t="s">
+        <v>1623</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="52" t="s">
+        <v>194</v>
+      </c>
+      <c r="B12" s="52" t="s">
+        <v>1624</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="52" t="s">
+        <v>1625</v>
+      </c>
+      <c r="B13" s="52" t="s">
+        <v>1887</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="52" t="s">
+        <v>1898</v>
+      </c>
+      <c r="B14" s="52" t="s">
+        <v>1626</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="52" t="s">
+        <v>1627</v>
+      </c>
+      <c r="B15" s="52" t="s">
+        <v>1628</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="52" t="s">
+        <v>1899</v>
+      </c>
+      <c r="B16" s="52" t="s">
+        <v>1629</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="52" t="s">
+        <v>1888</v>
+      </c>
+      <c r="B17" s="52" t="s">
+        <v>1630</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="52" t="s">
+        <v>1889</v>
+      </c>
+      <c r="B18" s="52" t="s">
+        <v>1631</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="52" t="s">
+        <v>1632</v>
+      </c>
+      <c r="B19" s="52" t="s">
+        <v>1633</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="52" t="s">
+        <v>1890</v>
+      </c>
+      <c r="B20" s="52" t="s">
+        <v>1634</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="52" t="s">
+        <v>2</v>
+      </c>
+      <c r="B21" s="52" t="s">
+        <v>1635</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="52" t="s">
+        <v>1891</v>
+      </c>
+      <c r="B22" s="52" t="s">
+        <v>1636</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="52" t="s">
+        <v>1637</v>
+      </c>
+      <c r="B23" s="52" t="s">
+        <v>1638</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="52" t="s">
+        <v>1639</v>
+      </c>
+      <c r="B24" s="52" t="s">
+        <v>1640</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="52" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B25" s="52" t="s">
+        <v>1642</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="52" t="s">
+        <v>1643</v>
+      </c>
+      <c r="B26" s="52" t="s">
+        <v>1644</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="52" t="s">
+        <v>1645</v>
+      </c>
+      <c r="B27" s="52" t="s">
+        <v>1646</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" s="52" t="s">
+        <v>1647</v>
+      </c>
+      <c r="B28" s="52" t="s">
+        <v>1648</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" s="52" t="s">
+        <v>1649</v>
+      </c>
+      <c r="B29" s="52" t="s">
+        <v>1650</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" s="52" t="s">
+        <v>224</v>
+      </c>
+      <c r="B30" s="52" t="s">
+        <v>1892</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" s="52" t="s">
+        <v>1651</v>
+      </c>
+      <c r="B31" s="52" t="s">
+        <v>1652</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" s="52" t="s">
+        <v>1655</v>
+      </c>
+      <c r="B32" s="52" t="s">
+        <v>1656</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="52" t="s">
+        <v>1653</v>
+      </c>
+      <c r="B33" s="52" t="s">
+        <v>1654</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" s="52" t="s">
+        <v>1659</v>
+      </c>
+      <c r="B34" s="52" t="s">
+        <v>1660</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" s="52" t="s">
+        <v>1657</v>
+      </c>
+      <c r="B35" s="52" t="s">
+        <v>1658</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" s="52" t="s">
+        <v>1662</v>
+      </c>
+      <c r="B36" s="52" t="s">
+        <v>1663</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" s="52" t="s">
+        <v>1667</v>
+      </c>
+      <c r="B37" s="52" t="s">
+        <v>1668</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" s="52" t="s">
+        <v>1900</v>
+      </c>
+      <c r="B38" s="52" t="s">
+        <v>1897</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" s="52" t="s">
+        <v>1893</v>
+      </c>
+      <c r="B39" s="52" t="s">
+        <v>1894</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" s="52" t="s">
+        <v>1665</v>
+      </c>
+      <c r="B40" s="52" t="s">
+        <v>1666</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" s="52" t="s">
+        <v>1901</v>
+      </c>
+      <c r="B41" s="52" t="s">
+        <v>1664</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" s="52" t="s">
+        <v>1669</v>
+      </c>
+      <c r="B42" s="52" t="s">
+        <v>1670</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" s="52" t="s">
+        <v>1034</v>
+      </c>
+      <c r="B43" s="52" t="s">
+        <v>1895</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" s="52" t="s">
+        <v>1671</v>
+      </c>
+      <c r="B44" s="52" t="s">
+        <v>1672</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" s="52" t="s">
+        <v>1896</v>
+      </c>
+      <c r="B45" s="52" t="s">
+        <v>1661</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" s="52" t="s">
+        <v>1673</v>
+      </c>
+      <c r="B46" s="52" t="s">
+        <v>1674</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" s="52" t="s">
+        <v>1675</v>
+      </c>
+      <c r="B47" s="52" t="s">
+        <v>1676</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" s="52" t="s">
+        <v>1677</v>
+      </c>
+      <c r="B48" s="52" t="s">
+        <v>1678</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" s="52" t="s">
+        <v>1679</v>
+      </c>
+      <c r="B49" s="52" t="s">
+        <v>1691</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" s="52" t="s">
+        <v>1680</v>
+      </c>
+      <c r="B50" s="52" t="s">
+        <v>1681</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" s="52" t="s">
+        <v>1682</v>
+      </c>
+      <c r="B51" s="52" t="s">
+        <v>1692</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" s="52" t="s">
+        <v>1683</v>
+      </c>
+      <c r="B52" s="52" t="s">
+        <v>1684</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" s="52" t="s">
+        <v>1685</v>
+      </c>
+      <c r="B53" s="52" t="s">
+        <v>1693</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" s="52" t="s">
+        <v>1686</v>
+      </c>
+      <c r="B54" s="52" t="s">
+        <v>1687</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" s="52" t="s">
+        <v>145</v>
+      </c>
+      <c r="B55" s="52" t="s">
+        <v>1694</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" s="52" t="s">
+        <v>1688</v>
+      </c>
+      <c r="B56" s="52" t="s">
+        <v>1689</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" s="52" t="s">
+        <v>1690</v>
+      </c>
+      <c r="B57" s="52" t="s">
+        <v>1695</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" s="52" t="s">
+        <v>1696</v>
+      </c>
+      <c r="B58" s="52" t="s">
+        <v>1697</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" s="52" t="s">
+        <v>336</v>
+      </c>
+      <c r="B59" s="52" t="s">
+        <v>1698</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" s="52" t="s">
+        <v>1699</v>
+      </c>
+      <c r="B60" s="52" t="s">
+        <v>1681</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" s="52" t="s">
+        <v>1700</v>
+      </c>
+      <c r="B61" s="52" t="s">
+        <v>1701</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" s="52" t="s">
+        <v>1702</v>
+      </c>
+      <c r="B62" s="52" t="s">
+        <v>1703</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63" s="52" t="s">
+        <v>1704</v>
+      </c>
+      <c r="B63" s="52" t="s">
+        <v>1708</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" s="52" t="s">
+        <v>1705</v>
+      </c>
+      <c r="B64" s="52" t="s">
+        <v>1706</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" s="52" t="s">
+        <v>1707</v>
+      </c>
+      <c r="B65" s="52" t="s">
+        <v>1709</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66" s="52" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B66" s="52" t="s">
+        <v>1710</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67" s="52" t="s">
+        <v>1052</v>
+      </c>
+      <c r="B67" s="52" t="s">
+        <v>1711</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68" s="52" t="s">
+        <v>1712</v>
+      </c>
+      <c r="B68" s="52" t="s">
+        <v>1713</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69" s="52" t="s">
+        <v>1714</v>
+      </c>
+      <c r="B69" s="52" t="s">
+        <v>1902</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70" s="52" t="s">
+        <v>1715</v>
+      </c>
+      <c r="B70" s="52" t="s">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71" s="52" t="s">
+        <v>1717</v>
+      </c>
+      <c r="B71" s="52" t="s">
+        <v>1881</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72" s="52" t="s">
+        <v>1718</v>
+      </c>
+      <c r="B72" s="52" t="s">
+        <v>1719</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" s="52" t="s">
+        <v>1720</v>
+      </c>
+      <c r="B73" s="52" t="s">
+        <v>1721</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" s="52" t="s">
+        <v>1669</v>
+      </c>
+      <c r="B74" s="52" t="s">
+        <v>1670</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" s="52" t="s">
+        <v>1722</v>
+      </c>
+      <c r="B75" s="52" t="s">
+        <v>1723</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" s="52" t="s">
+        <v>281</v>
+      </c>
+      <c r="B76" s="52" t="s">
+        <v>1724</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" s="52" t="s">
+        <v>217</v>
+      </c>
+      <c r="B77" s="52" t="s">
+        <v>1725</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" s="52" t="s">
+        <v>1726</v>
+      </c>
+      <c r="B78" s="52" t="s">
+        <v>1727</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" s="52" t="s">
+        <v>1730</v>
+      </c>
+      <c r="B79" s="52" t="s">
+        <v>1731</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" s="52" t="s">
+        <v>1734</v>
+      </c>
+      <c r="B80" s="52" t="s">
+        <v>1735</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" s="52" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B81" s="52" t="s">
+        <v>1739</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82" s="52" t="s">
+        <v>1728</v>
+      </c>
+      <c r="B82" s="52" t="s">
+        <v>1729</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83" s="52" t="s">
+        <v>1732</v>
+      </c>
+      <c r="B83" s="52" t="s">
+        <v>1733</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84" s="52" t="s">
+        <v>1736</v>
+      </c>
+      <c r="B84" s="52" t="s">
+        <v>1737</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85" s="52" t="s">
+        <v>1740</v>
+      </c>
+      <c r="B85" s="52" t="s">
+        <v>1741</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A1" location="Index!A1" display="Noun / Verb / Adjective"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -13757,39 +14938,39 @@
   <sheetData>
     <row r="1" spans="1:2" s="49" customFormat="1">
       <c r="A1" s="50" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="B1" s="50" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="51" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
       <c r="B2" s="51" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="51" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
       <c r="B3" s="51" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="51" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="B4" s="51" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="51" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="B5" s="51" t="s">
         <v>869</v>
@@ -13797,71 +14978,71 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="51" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="B6" s="51" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="51" t="s">
-        <v>1607</v>
+        <v>1608</v>
       </c>
       <c r="B7" s="51" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="51" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="B8" s="51" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="51" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="B9" s="51" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="51" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="B10" s="51" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="51" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
       <c r="B11" s="51" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="51" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
       <c r="B12" s="51" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="51" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
       <c r="B13" s="51" t="s">
-        <v>1577</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="51" t="s">
-        <v>1578</v>
+        <v>1579</v>
       </c>
       <c r="B14" s="51" t="s">
         <v>128</v>
@@ -13869,15 +15050,15 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="51" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="B15" s="51" t="s">
-        <v>1580</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="51" t="s">
-        <v>1581</v>
+        <v>1582</v>
       </c>
       <c r="B16" s="51" t="s">
         <v>891</v>
@@ -13885,87 +15066,87 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="51" t="s">
-        <v>1582</v>
+        <v>1583</v>
       </c>
       <c r="B17" s="51" t="s">
-        <v>1583</v>
+        <v>1584</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="51" t="s">
-        <v>1584</v>
+        <v>1585</v>
       </c>
       <c r="B18" s="51" t="s">
-        <v>1585</v>
+        <v>1586</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="51" t="s">
-        <v>1586</v>
+        <v>1587</v>
       </c>
       <c r="B19" s="51" t="s">
-        <v>1587</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="51" t="s">
-        <v>1588</v>
+        <v>1589</v>
       </c>
       <c r="B20" s="51" t="s">
-        <v>1589</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="51" t="s">
-        <v>1590</v>
+        <v>1591</v>
       </c>
       <c r="B21" s="51" t="s">
-        <v>1591</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="22" spans="1:2">
       <c r="A22" s="51" t="s">
-        <v>1592</v>
+        <v>1593</v>
       </c>
       <c r="B22" s="51" t="s">
-        <v>1593</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="51" t="s">
-        <v>1594</v>
+        <v>1595</v>
       </c>
       <c r="B23" s="51" t="s">
-        <v>1595</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" s="51" t="s">
-        <v>1596</v>
+        <v>1597</v>
       </c>
       <c r="B24" s="51" t="s">
-        <v>1599</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" s="51" t="s">
-        <v>1597</v>
+        <v>1598</v>
       </c>
       <c r="B25" s="51" t="s">
-        <v>1598</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" s="51" t="s">
+        <v>1602</v>
+      </c>
+      <c r="B26" s="51" t="s">
         <v>1601</v>
-      </c>
-      <c r="B26" s="51" t="s">
-        <v>1600</v>
       </c>
     </row>
     <row r="27" spans="1:2">
       <c r="A27" s="51" t="s">
-        <v>1602</v>
+        <v>1603</v>
       </c>
       <c r="B27" s="51" t="s">
         <v>900</v>
@@ -13973,18 +15154,18 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="51" t="s">
-        <v>1603</v>
+        <v>1604</v>
       </c>
       <c r="B28" s="51" t="s">
-        <v>1604</v>
+        <v>1605</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="51" t="s">
-        <v>1605</v>
+        <v>1606</v>
       </c>
       <c r="B29" s="51" t="s">
-        <v>1606</v>
+        <v>1607</v>
       </c>
     </row>
   </sheetData>
@@ -14004,7 +15185,7 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1">
       <c r="A1" s="27" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>591</v>
@@ -14012,26 +15193,26 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="28" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="B2" s="28" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="28" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="B3" s="28" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="28" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="B4" s="28" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="30">
@@ -14039,15 +15220,15 @@
         <v>252</v>
       </c>
       <c r="B5" s="28" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="28" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="B6" s="28" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -14055,12 +15236,12 @@
         <v>40</v>
       </c>
       <c r="B7" s="28" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="28" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="B8" s="28" t="s">
         <v>142</v>
@@ -14068,18 +15249,18 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="28" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B9" s="28" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="28" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="B10" s="28" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -14087,12 +15268,12 @@
         <v>214</v>
       </c>
       <c r="B11" s="28" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="28" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="B12" s="28" t="s">
         <v>869</v>
@@ -14100,10 +15281,10 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="28" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="B13" s="28" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -14111,23 +15292,23 @@
         <v>137</v>
       </c>
       <c r="B14" s="28" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="28" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="B15" s="28" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="28" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="B16" s="28" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -14135,31 +15316,31 @@
         <v>220</v>
       </c>
       <c r="B17" s="28" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="28" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B18" s="28" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="28" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="B19" s="28" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="28" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="B20" s="28" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -14167,7 +15348,7 @@
         <v>307</v>
       </c>
       <c r="B21" s="28" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -14220,18 +15401,18 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" s="30" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="B28" s="31" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
     </row>
     <row r="29" spans="1:2">
       <c r="A29" s="30" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="B29" s="31" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
     </row>
     <row r="30" spans="1:2">
@@ -14239,12 +15420,12 @@
         <v>155</v>
       </c>
       <c r="B30" s="31" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="30" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="B31" s="31" t="s">
         <v>189</v>
@@ -14252,10 +15433,10 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="30" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="B32" s="31" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
     </row>
     <row r="33" spans="1:2">
@@ -14268,10 +15449,10 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="30" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="B34" s="31" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
     </row>
     <row r="35" spans="1:2">
@@ -14303,7 +15484,7 @@
         <v>198</v>
       </c>
       <c r="B38" s="31" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
     </row>
     <row r="39" spans="1:2">
@@ -14316,7 +15497,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="30" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="B40" s="31" t="s">
         <v>239</v>
@@ -14324,10 +15505,10 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="30" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="B41" s="31" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
     </row>
     <row r="42" spans="1:2">
@@ -14343,7 +15524,7 @@
         <v>179</v>
       </c>
       <c r="B43" s="31" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
     </row>
     <row r="44" spans="1:2">
@@ -14351,20 +15532,20 @@
         <v>185</v>
       </c>
       <c r="B44" s="31" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="30" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="B45" s="31" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="30" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="B46" s="31" t="s">
         <v>230</v>
@@ -14375,15 +15556,15 @@
         <v>278</v>
       </c>
       <c r="B47" s="31" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="30" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="B48" s="31" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
     </row>
     <row r="49" spans="1:2">
@@ -14399,23 +15580,23 @@
         <v>204</v>
       </c>
       <c r="B50" s="31" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="30" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="B51" s="31" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="30" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="B52" s="31" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
     </row>
     <row r="53" spans="1:2">
@@ -14423,15 +15604,15 @@
         <v>208</v>
       </c>
       <c r="B53" s="31" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="30" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="B54" s="31" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
     </row>
     <row r="55" spans="1:2">
@@ -14439,7 +15620,7 @@
         <v>176</v>
       </c>
       <c r="B55" s="31" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
     </row>
     <row r="56" spans="1:2">
@@ -14447,15 +15628,15 @@
         <v>177</v>
       </c>
       <c r="B56" s="31" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="30" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="B57" s="31" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -14463,7 +15644,7 @@
         <v>163</v>
       </c>
       <c r="B58" s="31" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
     </row>
     <row r="59" spans="1:2">
@@ -14479,63 +15660,63 @@
         <v>218</v>
       </c>
       <c r="B60" s="31" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="30" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="B61" s="31" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="30" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="B62" s="31" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="30" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="B63" s="31" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="30" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="B64" s="31" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="30" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="B65" s="31" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="30" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="B66" s="31" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="30" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="B67" s="31" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
     </row>
     <row r="68" spans="1:2">
@@ -14548,18 +15729,18 @@
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="30" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="B69" s="31" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="30" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="B70" s="31" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="71" spans="1:2">
@@ -14572,15 +15753,15 @@
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="30" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="B72" s="31" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="30" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="B73" s="31" t="s">
         <v>138</v>
@@ -14588,7 +15769,7 @@
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="30" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="B74" s="31" t="s">
         <v>269</v>
@@ -14596,50 +15777,50 @@
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="30" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="B75" s="31" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="30" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="B76" s="31" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="30" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="B77" s="31" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="30" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="B78" s="31" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="30" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="B79" s="31" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="30" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="B80" s="31" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="81" spans="1:2">
@@ -14660,15 +15841,15 @@
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="30" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="B83" s="31" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="30" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="B84" s="31" t="s">
         <v>234</v>
@@ -14679,7 +15860,7 @@
         <v>178</v>
       </c>
       <c r="B85" s="31" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="86" spans="1:2">
@@ -14700,7 +15881,7 @@
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="30" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="B88" s="31" t="s">
         <v>237</v>
@@ -14716,18 +15897,18 @@
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="30" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="B90" s="31" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="30" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="B91" s="31" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="92" spans="1:2">
@@ -14740,10 +15921,10 @@
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="30" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B93" s="31" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="94" spans="1:2">
@@ -14772,15 +15953,15 @@
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="30" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="B97" s="31" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="30" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="B98" s="31" t="s">
         <v>206</v>
@@ -14788,50 +15969,50 @@
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="30" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="B99" s="31" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" s="30" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="B100" s="31" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" s="30" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="B101" s="31" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="30" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="B102" s="31" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="30" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="B103" s="31" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="30" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="B104" s="31" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="105" spans="1:2">
@@ -14839,12 +16020,12 @@
         <v>164</v>
       </c>
       <c r="B105" s="31" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" s="30" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="B106" s="31" t="s">
         <v>202</v>
@@ -14852,18 +16033,18 @@
     </row>
     <row r="107" spans="1:2">
       <c r="A107" s="30" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B107" s="31" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="30" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="B108" s="31" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="109" spans="1:2">
@@ -14879,15 +16060,15 @@
         <v>153</v>
       </c>
       <c r="B110" s="31" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="30" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="B111" s="31" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="112" spans="1:2">
@@ -14903,23 +16084,23 @@
         <v>186</v>
       </c>
       <c r="B113" s="31" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="30" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="B114" s="31" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="30" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="B115" s="31" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="116" spans="1:2">
@@ -14932,42 +16113,42 @@
     </row>
     <row r="117" spans="1:2">
       <c r="A117" s="30" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="B117" s="31" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" s="30" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="B118" s="31" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" s="30" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="B119" s="31" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="30" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="B120" s="31" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" s="30" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="B121" s="31" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
     </row>
   </sheetData>
@@ -14989,7 +16170,7 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1">
       <c r="A1" s="35" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>592</v>
@@ -15701,7 +16882,7 @@
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="36" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="B90" s="34" t="s">
         <v>139</v>
@@ -15735,10 +16916,10 @@
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1">
       <c r="A1" s="35" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -15967,226 +17148,226 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" s="34" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="B30" s="34" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
     </row>
     <row r="31" spans="1:2">
       <c r="A31" s="34" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="B31" s="34" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="32" spans="1:2">
       <c r="A32" s="48" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="B32" s="34" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="34" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="B33" s="34" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="34" spans="1:2">
       <c r="A34" s="34" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="B34" s="34" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="35" spans="1:2">
       <c r="A35" s="34" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="B35" s="34" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="36" spans="1:2">
       <c r="A36" s="34" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="B36" s="34" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
     </row>
     <row r="37" spans="1:2">
       <c r="A37" s="34" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="B37" s="34" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="38" spans="1:2">
       <c r="A38" s="48" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="B38" s="34" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="39" spans="1:2">
       <c r="A39" s="34" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="B39" s="34" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="34" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="B40" s="34" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="34" t="s">
+        <v>1398</v>
+      </c>
+      <c r="B41" s="34" t="s">
         <v>1397</v>
-      </c>
-      <c r="B41" s="34" t="s">
-        <v>1396</v>
       </c>
     </row>
     <row r="42" spans="1:2">
       <c r="A42" s="34" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="B42" s="34" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
     </row>
     <row r="43" spans="1:2">
       <c r="A43" s="34" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="B43" s="34" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="44" spans="1:2">
       <c r="A44" s="34" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="B44" s="34" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="34" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="B45" s="34" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
     </row>
     <row r="46" spans="1:2">
       <c r="A46" s="34" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="B46" s="34" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="47" spans="1:2">
       <c r="A47" s="34" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="B47" s="34" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
     </row>
     <row r="48" spans="1:2">
       <c r="A48" s="34" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="B48" s="34" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="34" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="B49" s="34" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="34" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="B50" s="34" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="34" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="B51" s="34" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="34" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="B52" s="34" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="34" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="B53" s="34" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="34" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="B54" s="34" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="34" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="B55" s="34" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="34" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="B56" s="34" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="34" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="B57" s="34" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="58" spans="1:2">
@@ -16194,527 +17375,527 @@
         <v>230</v>
       </c>
       <c r="B58" s="34" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="34" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="B59" s="34" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="34" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="B60" s="34" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="34" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="B61" s="34" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="34" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="B62" s="34" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="34" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="B63" s="34" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="34" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="B64" s="34" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" s="34" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="B65" s="34" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" s="34" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="B66" s="34" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" s="34" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="B67" s="34" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" s="34" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="B68" s="34" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" s="34" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="B69" s="34" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" s="34" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="B70" s="34" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" s="34" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="B71" s="34" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" s="34" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="B72" s="34" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" s="34" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="B73" s="34" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" s="34" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="B74" s="34" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="75" spans="1:2">
       <c r="A75" s="34" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="B75" s="34" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="76" spans="1:2">
       <c r="A76" s="34" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="B76" s="34" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="77" spans="1:2">
       <c r="A77" s="34" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="B77" s="34" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="78" spans="1:2">
       <c r="A78" s="34" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="B78" s="34" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="79" spans="1:2">
       <c r="A79" s="34" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="B79" s="34" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="80" spans="1:2">
       <c r="A80" s="34" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="B80" s="34" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
     </row>
     <row r="81" spans="1:2">
       <c r="A81" s="34" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="B81" s="34" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="82" spans="1:2">
       <c r="A82" s="34" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="B82" s="34" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="83" spans="1:2">
       <c r="A83" s="34" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="B83" s="34" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
     </row>
     <row r="84" spans="1:2">
       <c r="A84" s="34" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="B84" s="34" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="85" spans="1:2">
       <c r="A85" s="34" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="B85" s="34" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="86" spans="1:2">
       <c r="A86" s="34" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="B86" s="34" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
     </row>
     <row r="87" spans="1:2">
       <c r="A87" s="34" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="B87" s="34" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
     </row>
     <row r="88" spans="1:2">
       <c r="A88" s="34" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="B88" s="34" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="89" spans="1:2">
       <c r="A89" s="34" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="B89" s="34" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="90" spans="1:2">
       <c r="A90" s="34" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="B90" s="34" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="91" spans="1:2">
       <c r="A91" s="34" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="B91" s="34" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="92" spans="1:2">
       <c r="A92" s="34" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="B92" s="34" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="93" spans="1:2">
       <c r="A93" s="34" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="B93" s="34" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="94" spans="1:2">
       <c r="A94" s="34" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="B94" s="34" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
     </row>
     <row r="95" spans="1:2">
       <c r="A95" s="34" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="B95" s="34" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="96" spans="1:2">
       <c r="A96" s="34" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="B96" s="34" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
     </row>
     <row r="97" spans="1:2">
       <c r="A97" s="34" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="B97" s="34" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="98" spans="1:2">
       <c r="A98" s="34" t="s">
+        <v>1500</v>
+      </c>
+      <c r="B98" s="34" t="s">
         <v>1499</v>
-      </c>
-      <c r="B98" s="34" t="s">
-        <v>1498</v>
       </c>
     </row>
     <row r="99" spans="1:2">
       <c r="A99" s="34" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="B99" s="34" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="100" spans="1:2">
       <c r="A100" s="34" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="B100" s="34" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
     </row>
     <row r="101" spans="1:2">
       <c r="A101" s="34" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="B101" s="34" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="102" spans="1:2">
       <c r="A102" s="34" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
       <c r="B102" s="34" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
     </row>
     <row r="103" spans="1:2">
       <c r="A103" s="34" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
       <c r="B103" s="34" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="104" spans="1:2">
       <c r="A104" s="34" t="s">
+        <v>1511</v>
+      </c>
+      <c r="B104" s="34" t="s">
         <v>1510</v>
-      </c>
-      <c r="B104" s="34" t="s">
-        <v>1509</v>
       </c>
     </row>
     <row r="105" spans="1:2">
       <c r="A105" s="34" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
       <c r="B105" s="34" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="106" spans="1:2">
       <c r="A106" s="34" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="B106" s="34" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="107" spans="1:2">
       <c r="A107" s="34" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="B107" s="34" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="108" spans="1:2">
       <c r="A108" s="34" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="B108" s="34" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="109" spans="1:2">
       <c r="A109" s="34" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
       <c r="B109" s="34" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="110" spans="1:2">
       <c r="A110" s="34" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="B110" s="34" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="111" spans="1:2">
       <c r="A111" s="34" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="B111" s="34" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="112" spans="1:2">
       <c r="A112" s="34" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="B112" s="34" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
     </row>
     <row r="113" spans="1:2">
       <c r="A113" s="34" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
       <c r="B113" s="34" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="114" spans="1:2">
       <c r="A114" s="34" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="B114" s="34" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="115" spans="1:2">
       <c r="A115" s="34" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="B115" s="34" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="116" spans="1:2">
       <c r="A116" s="34" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
       <c r="B116" s="34" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="117" spans="1:2">
       <c r="A117" s="34" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
       <c r="B117" s="34" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="118" spans="1:2">
       <c r="A118" s="34" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
       <c r="B118" s="34" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
     </row>
     <row r="119" spans="1:2">
       <c r="A119" s="34" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
       <c r="B119" s="34" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
     </row>
     <row r="120" spans="1:2">
       <c r="A120" s="34" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
       <c r="B120" s="34" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="121" spans="1:2">
       <c r="A121" s="34" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="B121" s="34" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="122" spans="1:2">
       <c r="A122" s="34" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
       <c r="B122" s="34" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="123" spans="1:2">
       <c r="A123" s="34" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="B123" s="34" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
     </row>
     <row r="124" spans="1:2">
@@ -17130,162 +18311,162 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="40" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="B2" s="38" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="40" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="B3" s="38" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="40" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="B4" s="38" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="40" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="B5" s="38" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="40" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="B6" s="38" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="40" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="B7" s="38" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="40" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="B8" s="38" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="40" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="B9" s="38" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="40" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="B10" s="38" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="40" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="B11" s="38" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="40" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="B12" s="38" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="40" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="B13" s="38" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="40" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="40" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="B15" s="38" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="40" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="40" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="B17" s="38" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="40" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" s="40" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="B19" s="38" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" s="40" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="B20" s="38" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" s="40" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="B21" s="38" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="63" spans="2:2">
